--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5539,55 +5539,65 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>CAM-014</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
+          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lens pointer retaining bands</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>B0B5RR41CT</t>
+          <t>9262K203</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§9.5</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5596,16 +5606,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Base and adjuster plates</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5615,15 +5620,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5633,14 +5638,14 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5649,16 +5654,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mirror plate</t>
+          <t>Base and adjuster plates</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5668,15 +5673,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>B09D941GXR</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5693,7 +5698,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5702,25 +5707,30 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5734,14 +5744,14 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5754,7 +5764,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5764,7 +5774,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -5789,7 +5799,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5802,7 +5812,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5812,7 +5822,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -5837,7 +5847,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5850,22 +5860,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Spherical washers</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -5883,14 +5888,14 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5903,7 +5908,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5913,15 +5923,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5931,14 +5941,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5947,16 +5957,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Spring seat washers</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5966,11 +5971,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5991,7 +5996,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6000,16 +6005,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6019,15 +6024,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6037,14 +6042,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-011</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6052,14 +6057,17 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>3" Long Corner Bracket, aluminum</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6069,15 +6077,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6088,18 +6096,13 @@
       <c r="K101" t="inlineStr">
         <is>
           <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-011</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6107,17 +6110,14 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>6</v>
-      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -6150,14 +6150,14 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern; existing stock confirmed in hand.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6185,11 +6185,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>96659A134</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern.</t>
+          <t>Six installed for the revised three-fastener-per-bracket pattern; existing stock confirmed in hand.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-015</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6224,16 +6224,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6243,15 +6243,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6259,16 +6259,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Six installed for the revised three-fastener-per-bracket pattern.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-017</t>
+          <t>MIR-015</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6281,7 +6286,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6296,15 +6301,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6321,7 +6326,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-018</t>
+          <t>MIR-017</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6334,7 +6339,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6349,11 +6354,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6374,7 +6379,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-023</t>
+          <t>MIR-018</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6387,12 +6392,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; short-length option</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6402,11 +6407,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6418,21 +6423,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>MIR-023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; long-length option</t>
+          <t>Provisional quick-release plate mounting screw; short-length option</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6499,34 +6499,34 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>Provisional quick-release plate mounting screw; long-length option</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6541,14 +6541,14 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6561,22 +6561,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -6594,14 +6594,19 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6614,12 +6619,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Safety retainer padding</t>
+          <t>Mirror mounting</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6629,7 +6634,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8334K15</t>
+          <t>7587A25</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -6637,7 +6642,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6647,14 +6652,14 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6663,16 +6668,39 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ABS printed front safety retainers</t>
+          <t>Adhesive backed F1 felt</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Safety retainer padding</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8334K15</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6684,7 +6712,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MIR-022</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6693,69 +6721,46 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Primary structural-bracket screws</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>90585A997</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
-        <v>5</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>ABS printed front safety retainers</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Use six installed: two through the vertical plate and one through the base plate per bracket. Two 5-packs required; four spare.</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>MIR-022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Primary structural-bracket screws</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6765,15 +6770,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>91458A160</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6783,14 +6788,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Use six installed: two through the vertical plate and one through the base plate per bracket. Two 5-packs required; four spare.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6803,7 +6813,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6813,7 +6823,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -6838,7 +6848,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-002</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6851,17 +6861,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -6875,13 +6885,18 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>§9.5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6894,12 +6909,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Source-slit blade spacing</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6909,7 +6919,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -6923,18 +6933,13 @@
       <c r="J117" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6947,22 +6952,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -6980,14 +6985,14 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7000,12 +7005,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7015,7 +7020,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7040,7 +7045,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-007</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7048,14 +7053,35 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>18 AWG wire</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>LED mounting</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2979N13</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7065,14 +7091,14 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-008</t>
+          <t>SHP-007</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7082,7 +7108,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Heat-shrink tubing</t>
+          <t>18 AWG wire</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7093,13 +7119,18 @@
       <c r="J121" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-009</t>
+          <t>SHP-008</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7109,12 +7140,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>USB-C chargers/cables</t>
+          <t>Heat-shrink tubing</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>DP100 power</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7126,7 +7157,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-010</t>
+          <t>SHP-009</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7136,29 +7167,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thermal compound</t>
+          <t>USB-C chargers/cables</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LED heatsink interfaces</t>
+          <t>DP100 power</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-010</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7166,35 +7192,14 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
-      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>Thermal compound</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>1818A45</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>1</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED heatsink interfaces</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7204,19 +7209,14 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§§6.2, 7, 8.4, 10.4</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7229,22 +7229,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -7262,14 +7262,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§§6.2, 7, 8.4, 10.4</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-013</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7277,26 +7282,52 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Soldering tools / supplies</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Mirror mount releasing assembly surface</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>US Plastics</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-013</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7304,52 +7335,26 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>1</v>
-      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Soldering tools / supplies</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>B002IZFPQE</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>1</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7362,22 +7367,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ABS carriage sliding-interface lubricant</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -7395,19 +7400,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§8.4</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7420,17 +7420,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>ABS carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -7448,19 +7453,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7473,22 +7478,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>White lithium grease, NLGI #2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>2890A56</t>
+          <t>Lucas Oil Products</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7511,14 +7511,14 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7564,19 +7564,19 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7622,19 +7622,19 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7.</t>
+          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -7743,14 +7743,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7763,22 +7763,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7796,58 +7796,116 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>§§8, 8.7</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>SHP-022</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Fullcompass</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>01001-1210</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>§§8, 8.7</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>SHP-023</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="inlineStr">
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>M3 × 0.5 tap and 2.5 mm tap drill</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Tap SM1CP2M rear for heatsink screws</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>Specified</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>§6.2</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>Confirm whether already in shop stock before purchasing; vendor and SKU not yet chosen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L136"/>
-  <conditionalFormatting sqref="J2:J136">
+  <autoFilter ref="A1:L137"/>
+  <conditionalFormatting sqref="J2:J137">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lens pointer adjusters</t>
+          <t>Lens pointer adjusters and yoke joints</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>One per adjuster, set in the pointer shoe yoke bosses. One pack of 25 in hand; 21 spare.</t>
+          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Phone-specific rail shoe with an arm carrying the rest rod. Concept mock-up only.</t>
+          <t>Phone-specific rail shoe with an arm carrying the rest rod. Retainer and safety catch not yet designed.</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5245,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rail shoe with the two yokes that hold the four adjusters</t>
+          <t>Rail-shoe saddle that carries the two yokes</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Lens-specific. Concept mock-up only.</t>
+          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Working-stock assortment; rod diameters and cut lengths remain open.</t>
+          <t>Working-stock assortment. Model uses two groove rods of 3 mm diameter × 10 mm and one phone rest rod of 4 mm diameter × 20 mm; confirm the assortment has these diameters.</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Two identical collars for the 37 mm barrel. Concept mock-up only.</t>
+          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Shared common 100-pack. Provisional: one screw per collar.</t>
+          <t>Shared common 100-pack. One screw per collar.</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004). Provisional: one nut per collar.</t>
+          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
         </is>
       </c>
     </row>
@@ -5597,60 +5597,52 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>CAM-015</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>B0B5RR41CT</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>ABS printed lens pointer yokes</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Carry the adjuster inserts and the retaining-band pegs</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§9.5</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Printed on their side; each bolted to the pointer shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>CAM-016</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5658,26 +5650,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Base and adjuster plates</t>
+          <t>Yoke-to-shoe joint screws</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>92125A208</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5686,19 +5678,24 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§§9.5, 9.7</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>10 mm head, 3 mm hex drive. Each screws up through the pointer shoe deck into a heat-set insert in the yoke foot.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5711,12 +5708,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Mirror plate</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5726,7 +5718,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -5744,14 +5736,14 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5760,29 +5752,34 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Base and adjuster plates</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>B09D941GXR</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5792,14 +5789,14 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5808,25 +5805,30 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5840,14 +5842,14 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5860,7 +5862,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5870,7 +5872,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -5895,7 +5897,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5908,22 +5910,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Spherical washers</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -5941,14 +5938,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5961,25 +5958,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5989,14 +5986,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6005,16 +6002,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Spring seat washers</t>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6024,15 +6021,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6042,14 +6039,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6058,16 +6055,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6077,15 +6069,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6095,14 +6087,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-011</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6110,14 +6102,17 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C102" t="n">
+        <v>6</v>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6127,11 +6122,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6145,19 +6140,14 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6166,11 +6156,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>3" Long Corner Bracket, aluminum</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6185,15 +6175,15 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6204,18 +6194,13 @@
       <c r="K103" t="inlineStr">
         <is>
           <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern; existing stock confirmed in hand.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-011</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6223,17 +6208,14 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>6</v>
-      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6243,11 +6225,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>96659A134</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6266,14 +6248,14 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-015</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6282,16 +6264,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6301,15 +6283,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6317,16 +6299,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Six installed for the revised three-fastener-per-bracket pattern; existing stock confirmed in hand.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-017</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6335,16 +6322,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6354,11 +6341,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6370,16 +6357,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Six installed for the revised three-fastener-per-bracket pattern.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-018</t>
+          <t>MIR-015</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6392,7 +6384,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6407,15 +6399,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6432,7 +6424,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-023</t>
+          <t>MIR-017</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6445,12 +6437,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; short-length option</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6460,11 +6452,11 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6476,21 +6468,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>MIR-018</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6503,12 +6490,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; long-length option</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6518,11 +6505,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6534,21 +6521,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>MIR-023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6557,34 +6539,34 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>Provisional quick-release plate mounting screw; short-length option</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6599,14 +6581,14 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6615,16 +6597,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>Provisional quick-release plate mounting screw; long-length option</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6634,15 +6616,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6652,14 +6634,19 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6672,22 +6659,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Safety retainer padding</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8334K15</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -6695,7 +6682,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6705,14 +6692,19 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6721,28 +6713,51 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ABS printed front safety retainers</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Mirror mounting</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>7587A25</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MIR-022</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6751,16 +6766,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>Adhesive backed F1 felt</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Primary structural-bracket screws</t>
+          <t>Safety retainer padding</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6770,15 +6785,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>8334K15</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6788,80 +6803,62 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Use six installed: two through the vertical plate and one through the base plate per bracket. Two 5-packs required; four spare.</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>91458A160</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>ABS printed front safety retainers</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>MIR-022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Primary structural-bracket screws</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6871,15 +6868,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6889,14 +6886,19 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Use six installed: two through the vertical plate and one through the base plate per bracket. Two 5-packs required; four spare.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6909,17 +6911,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -6933,13 +6935,18 @@
       <c r="J117" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>§9.5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-002</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6952,22 +6959,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Source-slit blade spacing</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -6985,14 +6987,14 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§7.4</t>
+          <t>§9.5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7005,22 +7007,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M2 tap</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7034,18 +7031,13 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7058,22 +7050,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -7091,14 +7083,14 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-007</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7106,14 +7098,35 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>18 AWG wire</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>LED board mounting into SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>8305A78</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7123,14 +7136,14 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-008</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7138,26 +7151,52 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Heat-shrink tubing</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>LED mounting</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2979N13</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-009</t>
+          <t>SHP-007</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7167,24 +7206,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>USB-C chargers/cables</t>
+          <t>18 AWG wire</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>DP100 power</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-010</t>
+          <t>SHP-008</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7194,29 +7238,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thermal compound</t>
+          <t>Heat-shrink tubing</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LED heatsink interfaces</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-009</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7224,57 +7263,26 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>1</v>
-      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>USB-C chargers/cables</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>1818A45</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>1</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>DP100 power</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>§§6.2, 7, 8.4, 10.4</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-010</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7282,35 +7290,14 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>1</v>
-      </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>Thermal compound</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>US Plastics</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>46489</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>1</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED heatsink interfaces</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7320,14 +7307,14 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-013</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7335,26 +7322,57 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Soldering tools / supplies</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1818A45</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>§§6.2, 7, 8.4, 10.4</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7367,22 +7385,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
+          <t>Mirror mount releasing assembly surface</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>US Plastics</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>B002IZFPQE</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -7400,14 +7418,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-013</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7415,57 +7433,26 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>1</v>
-      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>Soldering tools / supplies</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ABS carriage sliding-interface lubricant</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>1418K51</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>1</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>§8.4</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7478,17 +7465,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7506,19 +7498,14 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>§10.4</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7531,12 +7518,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>ABS carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7546,7 +7533,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2890A56</t>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7564,19 +7551,19 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7589,22 +7576,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>White lithium grease, NLGI #2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>2890A58</t>
+          <t>Lucas Oil Products</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7622,19 +7604,19 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7647,12 +7629,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7662,7 +7644,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -7680,19 +7662,19 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7705,12 +7687,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7720,7 +7702,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -7738,19 +7720,19 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7763,12 +7745,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7778,7 +7760,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -7801,14 +7783,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7821,22 +7803,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -7844,7 +7826,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7854,58 +7836,174 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>§§8, 8.7</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>SHP-021</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>91458A115</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SHP-022</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Fullcompass</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>01001-1210</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>§§8, 8.7</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>SHP-023</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="inlineStr">
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
         <is>
           <t>M3 × 0.5 tap and 2.5 mm tap drill</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Tap SM1CP2M rear for heatsink screws</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>Specified</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>§6.2</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>Confirm whether already in shop stock before purchasing; vendor and SKU not yet chosen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L137"/>
-  <conditionalFormatting sqref="J2:J137">
+  <autoFilter ref="A1:L139"/>
+  <conditionalFormatting sqref="J2:J139">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -2649,7 +2649,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2991,6 +2991,9 @@
           <t>Light source</t>
         </is>
       </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>M3 × 6 mm socket head screw</t>
@@ -3013,12 +3016,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>§6.2</t>
+          <t>§§6.2, 6.4</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Provisional length (3 mm base + ~2.5 mm thread into cap). Quantity per module (2–3) and SKU to be confirmed; check existing M3 stock.</t>
+          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). SKU to be confirmed; check existing M3 stock.</t>
         </is>
       </c>
     </row>
@@ -7139,6 +7142,11 @@
           <t>§6.4</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7808,7 +7816,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7836,12 +7844,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
@@ -7977,33 +7985,167 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>M3 × 0.5 tap and 2.5 mm tap drill</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tap SM1CP2M rear for heatsink screws</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>8305A32</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>§6.2</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Confirm whether already in shop stock before purchasing; vendor and SKU not yet chosen.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SHP-025</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2979N15</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SHP-026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2979N14</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L139"/>
-  <conditionalFormatting sqref="J2:J139">
+  <autoFilter ref="A1:L141"/>
+  <conditionalFormatting sqref="J2:J141">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern; existing stock confirmed in hand.</t>
+          <t>Eight installed, four per bracket; existing stock was confirmed in hand for six, so confirm two more.</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Six installed for the revised three-fastener-per-bracket pattern.</t>
+          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
@@ -6851,9 +6851,6 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>6</v>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
@@ -6861,7 +6858,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Primary structural-bracket screws</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6894,27 +6891,32 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Use six installed: two through the vertical plate and one through the base plate per bracket. Two 5-packs required; four spare.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>MIR-026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
+          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Bracket screws, heads on the bracket</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6924,32 +6926,37 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>91458A160</t>
+          <t>98164A527</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Four per bracket, two through the plate and two through the base; eight installed, so order two 5-packs (two spare). 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6962,7 +6969,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6972,7 +6979,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -6997,7 +7004,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-002</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7010,17 +7017,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7034,13 +7041,18 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>§9.5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7053,12 +7065,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Source-slit blade spacing</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7068,7 +7075,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -7082,18 +7089,13 @@
       <c r="J120" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7106,22 +7108,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -7139,19 +7141,14 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7164,12 +7161,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7179,7 +7176,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -7198,13 +7195,18 @@
       <c r="K122" t="inlineStr">
         <is>
           <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-007</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7212,14 +7214,35 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>18 AWG wire</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>LED mounting</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2979N13</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7229,14 +7252,14 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-008</t>
+          <t>SHP-007</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7246,7 +7269,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Heat-shrink tubing</t>
+          <t>18 AWG wire</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7257,13 +7280,18 @@
       <c r="J124" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-009</t>
+          <t>SHP-008</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7273,12 +7301,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>USB-C chargers/cables</t>
+          <t>Heat-shrink tubing</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>DP100 power</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7290,7 +7318,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-010</t>
+          <t>SHP-009</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7300,29 +7328,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Thermal compound</t>
+          <t>USB-C chargers/cables</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LED heatsink interfaces</t>
+          <t>DP100 power</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-010</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7330,35 +7353,14 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>1</v>
-      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>Thermal compound</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>1818A45</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>1</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED heatsink interfaces</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7368,19 +7370,14 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>§§6.2, 7, 8.4, 10.4</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7393,22 +7390,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -7426,14 +7423,19 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§§6.2, 7, 8.4, 10.4</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-013</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7441,26 +7443,52 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Soldering tools / supplies</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Mirror mount releasing assembly surface</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>US Plastics</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-013</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7468,52 +7496,26 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>1</v>
-      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Soldering tools / supplies</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>B002IZFPQE</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>1</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7526,22 +7528,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ABS carriage sliding-interface lubricant</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7559,19 +7561,14 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§8.4</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7584,17 +7581,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>ABS carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7612,19 +7614,19 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7637,22 +7639,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>White lithium grease, NLGI #2</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2890A56</t>
+          <t>Lucas Oil Products</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -7675,14 +7672,14 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7695,12 +7692,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7710,7 +7707,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -7728,19 +7725,19 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7753,12 +7750,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7768,7 +7765,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -7786,19 +7783,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7811,12 +7808,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7826,7 +7823,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -7844,19 +7841,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>§§6.4, 10.9</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7869,12 +7866,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7884,7 +7881,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -7902,19 +7899,19 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7927,22 +7924,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -7950,7 +7947,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7960,19 +7957,19 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>§§8, 8.7</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7985,22 +7982,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Fullcompass</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>01001-1210</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -8008,29 +8005,29 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§8, 8.7</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SHP-025</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8043,12 +8040,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8058,7 +8055,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2979N15</t>
+          <t>8305A32</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -8081,71 +8078,129 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>SHP-025</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2979N15</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>SHP-026</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
         <is>
           <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>Lead holes through SM1CP2M cap and heatsink base</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>McMaster</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>2979N14</t>
         </is>
       </c>
-      <c r="H141" t="n">
-        <v>1</v>
-      </c>
-      <c r="I141" t="inlineStr">
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>each</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>To procure</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>§6.4</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t>Same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L141"/>
-  <conditionalFormatting sqref="J2:J141">
+  <autoFilter ref="A1:L142"/>
+  <conditionalFormatting sqref="J2:J142">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -8217,6 +8217,11 @@
       <formula>"CAD open"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J142" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CAD in src/schlieren/parts/slit_head.py; first test print successful (fits and flexure motion confirmed, §7.7).</t>
+          <t>CAD in src/schlieren/parts/slit_head.py; printed and evaluated, fit for purpose (§7.7).</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5337,30 +5337,30 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Stainless steel round rod assortment, 100 mm length</t>
+          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Groove rods at the fourth lens-pointer screw; phone rest rod</t>
+          <t>Groove rods at the fourth lens-pointer screw</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>B08N4TSNPW</t>
+          <t>91585A351</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Working-stock assortment. Model uses two groove rods of 3 mm diameter × 10 mm and one phone rest rod of 4 mm diameter × 20 mm; confirm the assortment has these diameters.</t>
+          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
         </is>
       </c>
     </row>
@@ -5698,12 +5698,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>CAM-017</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5711,42 +5711,52 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
+          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Phone rest rod</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>B0B5RR41CT</t>
+          <t>91585A457</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§9.6</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5755,16 +5765,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Base and adjuster plates</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5774,15 +5779,15 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5792,14 +5797,14 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5808,16 +5813,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mirror plate</t>
+          <t>Base and adjuster plates</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5827,15 +5832,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>B09D941GXR</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5852,7 +5857,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5861,25 +5866,30 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5893,14 +5903,14 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5913,7 +5923,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5923,7 +5933,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -5948,7 +5958,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5961,7 +5971,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5971,7 +5981,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -5996,7 +6006,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6009,22 +6019,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Spherical washers</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -6042,14 +6047,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6062,7 +6067,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6072,15 +6082,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6090,14 +6100,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6106,16 +6116,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Spring seat washers</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6125,11 +6130,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6150,7 +6155,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6159,16 +6164,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6178,15 +6183,15 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6196,14 +6201,14 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-011</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6211,14 +6216,17 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>3" Long Corner Bracket, aluminum</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6228,15 +6236,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6247,18 +6255,13 @@
       <c r="K104" t="inlineStr">
         <is>
           <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-011</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6266,17 +6269,14 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>8</v>
-      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -6309,14 +6309,14 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Eight installed, four per bracket; existing stock was confirmed in hand for six, so confirm two more.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6344,11 +6344,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>96659A134</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6367,14 +6367,14 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Eight installed, one under each bracket locknut.</t>
+          <t>Eight installed, four per bracket; existing stock was confirmed in hand for six, so confirm two more.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-015</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6402,15 +6402,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6418,16 +6418,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-017</t>
+          <t>MIR-015</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6440,7 +6445,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6455,15 +6460,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6480,7 +6485,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIR-018</t>
+          <t>MIR-017</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6493,7 +6498,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6508,11 +6513,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6533,7 +6538,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIR-023</t>
+          <t>MIR-018</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6546,12 +6551,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; short-length option</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6561,11 +6566,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6577,21 +6582,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>MIR-023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; long-length option</t>
+          <t>Provisional quick-release plate mounting screw; short-length option</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6658,34 +6658,34 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>Provisional quick-release plate mounting screw; long-length option</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6700,14 +6700,14 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
+          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6720,22 +6720,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -6753,14 +6753,19 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6773,12 +6778,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Safety retainer padding</t>
+          <t>Mirror mounting</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6788,7 +6793,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8334K15</t>
+          <t>7587A25</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -6796,7 +6801,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6806,14 +6811,14 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6822,16 +6827,39 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ABS printed front safety retainers</t>
+          <t>Adhesive backed F1 felt</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Safety retainer padding</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>8334K15</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6843,7 +6871,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MIR-022</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6851,54 +6879,29 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Existing alternate bracket screw stock</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>90585A997</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>5</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>ABS printed front safety retainers</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MIR-026</t>
+          <t>MIR-022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6906,17 +6909,14 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>8</v>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bracket screws, heads on the bracket</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>98164A527</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -6949,27 +6949,32 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Four per bracket, two through the plate and two through the base; eight installed, so order two 5-packs (two spare). 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>MIR-026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
+          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Bracket screws, heads on the bracket</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6979,32 +6984,37 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>91458A160</t>
+          <t>98164A527</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Four per bracket, two through the plate and two through the base; eight installed, so order two 5-packs (two spare). 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7017,7 +7027,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7027,7 +7037,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7052,7 +7062,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7065,17 +7075,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -7089,13 +7099,18 @@
       <c r="J120" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>§9.5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7108,12 +7123,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Source-slit blade spacing</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7123,7 +7133,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -7137,18 +7147,13 @@
       <c r="J121" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7161,22 +7166,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -7194,19 +7199,14 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -7253,13 +7253,18 @@
       <c r="K123" t="inlineStr">
         <is>
           <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-007</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7267,14 +7272,35 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>18 AWG wire</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>LED mounting</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2979N13</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7284,14 +7310,14 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-008</t>
+          <t>SHP-007</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7301,7 +7327,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Heat-shrink tubing</t>
+          <t>18 AWG wire</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7312,13 +7338,18 @@
       <c r="J125" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-009</t>
+          <t>SHP-008</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7328,12 +7359,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>USB-C chargers/cables</t>
+          <t>Heat-shrink tubing</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>DP100 power</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7345,7 +7376,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-010</t>
+          <t>SHP-009</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7355,29 +7386,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Thermal compound</t>
+          <t>USB-C chargers/cables</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LED heatsink interfaces</t>
+          <t>DP100 power</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-010</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7385,35 +7411,14 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
-      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>Thermal compound</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>1818A45</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
-        <v>1</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED heatsink interfaces</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7423,19 +7428,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§§6.2, 7, 8.4, 10.4</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7448,22 +7448,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -7481,14 +7481,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§§6.2, 7, 8.4, 10.4</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-013</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7496,26 +7501,52 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Soldering tools / supplies</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Mirror mount releasing assembly surface</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>US Plastics</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-013</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7523,52 +7554,26 @@
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>1</v>
-      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Soldering tools / supplies</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>B002IZFPQE</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>LED wiring</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7581,22 +7586,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ABS carriage sliding-interface lubricant</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7614,19 +7619,14 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§8.4</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7639,17 +7639,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>ABS carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -7667,19 +7672,19 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7692,22 +7697,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>White lithium grease, NLGI #2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>2890A56</t>
+          <t>Lucas Oil Products</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -7783,19 +7783,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -7841,19 +7841,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -7899,19 +7899,19 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>§§6.4, 10.9</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -7957,19 +7957,19 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7982,22 +7982,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8015,19 +8015,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>§§8, 8.7</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8040,22 +8040,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Fullcompass</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>01001-1210</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -8063,29 +8063,29 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§8, 8.7</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SHP-025</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2979N15</t>
+          <t>8305A32</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -8136,71 +8136,129 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>SHP-025</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2979N15</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>SHP-026</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Shop supplies</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" t="inlineStr">
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>Lead holes through SM1CP2M cap and heatsink base</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>McMaster</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>2979N14</t>
         </is>
       </c>
-      <c r="H142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I142" t="inlineStr">
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>each</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>To procure</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>§6.4</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>Same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L142"/>
-  <conditionalFormatting sqref="J2:J142">
+  <autoFilter ref="A1:L143"/>
+  <conditionalFormatting sqref="J2:J143">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -8218,7 +8276,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J142" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J143" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8256,9 +8256,120 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SHP-027</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>8915N111</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter; how the adapter mates with the iron and with SHP-002 is unverified. Used with the Hakko iron SHP-028; set ABS installation near 250–265 °C, no higher than 280 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SHP-028</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Hakko FX888DX-10 soldering station</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Heat-set insert installation (CAM-005)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>FX888DX-10</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Ordered 2026-10-08; vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; adapter fit to SHP-002 unverified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L143"/>
-  <conditionalFormatting sqref="J2:J143">
+  <autoFilter ref="A1:L145"/>
+  <conditionalFormatting sqref="J2:J145">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -8276,7 +8387,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J143" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ABS printed post shoes</t>
+          <t>PLA printed post shoes</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M3 × 6 mm socket head screw</t>
+          <t>M3 × 0.5 × 6 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,9 +3009,22 @@
           <t>McMaster</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>91292A111</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3021,7 +3034,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). SKU to be confirmed; check existing M3 stock.</t>
+          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw; no 6 mm screws in stock.</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3576,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ABS printed flexure slit head</t>
+          <t>PLA printed flexure slit head</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3598,7 +3611,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ABS printed slit-head spigot adapter</t>
+          <t>PLA printed slit-head spigot adapter</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3628,7 +3641,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ABS printed slit-head blade clamp bars</t>
+          <t>PLA printed slit-head blade clamp bars</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4048,7 +4061,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABS printed carriage bodies</t>
+          <t>PLA printed carriage bodies</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4121,7 +4134,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven ABS plunger of the cutoff carriage.</t>
+          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4154,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ABS printed open-center keeper frames</t>
+          <t>PLA printed open-center keeper frames</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4219,7 +4232,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Reuse common M3 × 12 mm stock. Heads bear directly on ABS in ~0.5 mm recesses; tighten only to a light snug; verify printed fit.</t>
+          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug; verify printed fit.</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4290,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm ABS floor above pocket.</t>
+          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4310,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ABS printed cassettes</t>
+          <t>PLA printed cassettes</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4428,7 +4441,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Provisional 14 mm length; fit-test with 4 mm bar.</t>
+          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5216,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ABS printed phone rest</t>
+          <t>PLA printed phone rest</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5243,7 +5256,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ABS printed lens pointer shoe</t>
+          <t>PLA printed lens pointer shoe</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5369,7 +5382,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5399,7 +5412,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ABS printed lens collars</t>
+          <t>PLA printed lens collars</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5583,7 +5596,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5613,7 +5626,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ABS printed lens pointer yokes</t>
+          <t>PLA printed lens pointer yokes</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5681,7 +5694,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5739,7 +5752,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6367,7 +6380,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Eight installed, four per bracket; existing stock was confirmed in hand for six, so confirm two more.</t>
+          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6897,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ABS printed front safety retainers</t>
+          <t>PLA printed front safety retainers</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6997,7 +7010,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7486,7 +7499,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for ABS/metal calibration tacks and captive screw retention. No accelerator required.</t>
+          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for PLA/metal calibration tacks and captive screw retention. No accelerator required.</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7657,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ABS carriage sliding-interface lubricant</t>
+          <t>PLA carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7677,7 +7690,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Use only a trace film on dressed ABS-on-ABS sliding interfaces.</t>
+          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8139,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8184,7 +8197,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8252,7 +8265,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Same series as the 1.6 mm drill SHP-006.</t>
+          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8313,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8310,7 +8323,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter; how the adapter mates with the iron and with SHP-002 is unverified. Used with the Hakko iron SHP-028; set ABS installation near 250–265 °C, no higher than 280 °C.</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter; how the adapter mates with the iron and with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8366,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -5047,7 +5047,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lens pointer adjusters</t>
+          <t>Lens cradle adjusters</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lens pointer adjusters and yoke joints</t>
+          <t>Lens cradle adjusters and yoke joints</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lens pointer adjuster handwheels</t>
+          <t>Lens cradle adjuster handwheels</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PLA printed lens pointer shoe</t>
+          <t>PLA printed lens cradle shoe</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hard bearing pads under three lens-pointer screw tips</t>
+          <t>Hard bearing pads under three lens-cradle screw tips</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Groove rods at the fourth lens-pointer screw</t>
+          <t>Groove rods at the fourth lens-cradle screw</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lens pointer retaining bands</t>
+          <t>Lens cradle retaining bands</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PLA printed lens pointer yokes</t>
+          <t>PLA printed lens cradle yokes</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Printed on their side; each bolted to the pointer shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
+          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>10 mm head, 3 mm hex drive. Each screws up through the pointer shoe deck into a heat-set insert in the yoke foot.</t>
+          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTA(BOM!A2:A1000)</f>
+        <f>COUNTA(BOM!A:A)-1</f>
         <v/>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -2904,6 +2904,9 @@
           <t>SM1CP2M</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>each</t>
@@ -2911,7 +2914,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3024,7 +3027,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5382,7 +5385,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5596,7 +5599,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5694,7 +5697,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5752,7 +5755,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7010,7 +7013,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8139,7 +8142,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8197,7 +8200,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8313,7 +8316,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8323,7 +8326,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter; how the adapter mates with the iron and with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed); how it mates with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8369,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8376,7 +8379,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Ordered 2026-10-08; vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; adapter fit to SHP-002 unverified.</t>
+          <t>Ordered 2026-10-08; vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DP11 connection</t>
+          <t>DP100 connection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>One per LED module. Drill/tap: M2 board holes (front), M3 heatsink holes (rear, ~2.5 mm deep), lead pass-through holes at r ≈ 11 mm.</t>
+          <t>One per LED module. Drill/tap, all through holes (§6.4): M2 board holes, M3 heatsink holes, lead pass-through holes at r = 11.0 mm.</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw; no 6 mm screws in stock.</t>
+          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw.</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>§§7.3–7.4</t>
+          <t>§7.7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug; verify printed fit.</t>
+          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.8</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
+          <t>Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Order one pack. Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
+          <t>Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. Exact removable-plate hole pattern and final M4 screw length to be verified on arrival.</t>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Four per bracket, two through the plate and two through the base; eight installed, so order two 5-packs (two spare). 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
+          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§§6.2, 7, 8.4, 10.4</t>
+          <t>§§8.3, 8.4, 8.7, 10.4</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Use with 3.3 mm tap drill; exact hole locations await measurement of the delivered plate.</t>
+          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>§§8, 8.7</t>
+          <t>§§8.6, 8.7</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025). Confirm no M3 tap already in shop stock.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Ordered 2026-10-08; vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
+          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -1286,6 +1286,11 @@
           <t>§4.3</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Shared stock with FRM-011: two 10-packs in hand, 12 allocated (4 here, 8 on the yaw clamps); 8 spare.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1496,6 +1501,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>§4.3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Shared stock with FRM-007: two 10-packs in hand, 12 allocated (8 here, 4 on the rail pivots); 8 spare.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -2332,6 +2332,11 @@
           <t>Internally SM1-threaded end cap</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Transport cover for the condenser/iris assembly</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Thorlabs</t>
@@ -2357,7 +2362,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>§6.1</t>
+          <t>§6.7</t>
         </is>
       </c>
     </row>
@@ -2380,6 +2385,11 @@
           <t>Snap-on plastic dust cap for SM1 lens tube</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Transport cover for the condenser/iris assembly</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Thorlabs</t>
@@ -2405,7 +2415,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>§6.1</t>
+          <t>§6.7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>One of the pack of five is used; the rest are spare.</t>
         </is>
       </c>
     </row>
@@ -3602,11 +3617,6 @@
           <t>§7.2</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>CAD in src/schlieren/parts/slit_head.py; printed and evaluated, fit for purpose (§7.7).</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4319,7 +4329,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4338,7 +4348,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The source slit no longer uses a cassette (§7); quantity to be re-confirmed for the cutoff cassettes.</t>
+          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
         </is>
       </c>
     </row>
@@ -6466,9 +6476,6 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>4</v>
-      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>1/4"-20 × 1-1/2" flat-head screws</t>
@@ -6519,9 +6526,6 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>4</v>
-      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>1/4"-20 flex-top locknuts</t>
@@ -6572,9 +6576,6 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>4</v>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>1/4" thin washers</t>
@@ -6625,9 +6626,6 @@
           <t>Mirror cell</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>4</v>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
@@ -6635,7 +6633,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; short-length option</t>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6661,14 +6659,9 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-024.</t>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6686,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Provisional quick-release plate mounting screw; long-length option</t>
+          <t>Quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6726,7 +6719,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Four screws are the provisional installed quantity if this length matches the measured CAMVATE plate thickness; otherwise use MIR-023.</t>
+          <t>Four installed.</t>
         </is>
       </c>
     </row>
@@ -6893,6 +6886,11 @@
           <t>§10.8</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7512,7 +7510,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for spherical-washer sockets; use needle-sized localized drops for PLA/metal calibration tacks and captive screw retention. No accelerator required.</t>
+          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8044,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Apply only after fit and screw length are validated; preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8391,9 +8391,125 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SHP-029</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>27445A201</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>On order</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SHP-030</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Backup hole spotter; spots the cap and heatsink holes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2915A11</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>On order</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L145"/>
-  <conditionalFormatting sqref="J2:J145">
+  <autoFilter ref="A1:L147"/>
+  <conditionalFormatting sqref="J2:J147">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -8411,7 +8527,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J147" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -8435,7 +8435,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -64,7 +64,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -104,6 +104,13 @@
           <bgColor rgb="FFEAD8FF"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="medium">
+          <color rgb="FF808080"/>
+        </top>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -729,6 +736,17 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>COUNTIF(BOM!B:B,D20)</f>
+        <v/>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -837,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2054,7 +2072,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2533,7 +2551,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LGT-010</t>
+          <t>LGT-011</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2541,32 +2559,35 @@
           <t>Light source</t>
         </is>
       </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>92095A452</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2574,16 +2595,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LGT-011</t>
+          <t>LGT-012</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2596,12 +2617,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
+          <t>M2 nylon washers</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
+          <t>LED insulating washers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2611,11 +2632,8 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>92095A452</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>25</v>
+          <t>91545A410</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2636,7 +2654,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LGT-012</t>
+          <t>LGT-013</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2645,31 +2663,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M2 nylon washers</t>
+          <t>ALIENTEK DP100 DC Power Supply Variable, 30V 5A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LED insulating washers</t>
+          <t>LED CC/CV power supply</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>91545A410</t>
-        </is>
+          <t>B0CWRG6YFM</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2679,14 +2700,14 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LGT-013</t>
+          <t>LGT-014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2695,30 +2716,30 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ALIENTEK DP100 DC Power Supply Variable, 30V 5A</t>
+          <t>Cable Assembly, Micro-Fit 3.0 P-S 2ckt 150 mm</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LED CC/CV power supply</t>
+          <t>LED pigtails</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Mouser</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B0CWRG6YFM</t>
+          <t>538-214758-1021</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2739,7 +2760,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LGT-014</t>
+          <t>LGT-015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2748,16 +2769,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cable Assembly, Micro-Fit 3.0 P-S 2ckt 150 mm</t>
+          <t>Cable Assembly, Micro-Fit 3.0 R-S 2ckt 600MM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LED pigtails</t>
+          <t>Power supply pigtail</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2767,7 +2788,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>538-214758-1021</t>
+          <t>538-214756-1023</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2792,7 +2813,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LGT-015</t>
+          <t>LGT-016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2805,12 +2826,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cable Assembly, Micro-Fit 3.0 R-S 2ckt 600MM</t>
+          <t>Banana plug set 1 blk 1 red</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Power supply pigtail</t>
+          <t>DP100 connection</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2820,11 +2841,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>538-214756-1023</t>
+          <t>565-1825-02</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2845,7 +2866,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LGT-016</t>
+          <t>LGT-017</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2854,26 +2875,26 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Banana plug set 1 blk 1 red</t>
+          <t>SM1 end cap, external threads, with center drill mark, anodized aluminum</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DP100 connection</t>
+          <t>LED carrier: board on front face, threads into condenser SMR1/M</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mouser</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>565-1825-02</t>
+          <t>SM1CP2M</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2891,14 +2912,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>One per LED module. Drill/tap, all through holes (§6.4): M2 board holes, M3 heatsink holes, lead pass-through holes at r = 11.0 mm.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LGT-017</t>
+          <t>LGT-018</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2911,26 +2937,23 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SM1 end cap, external threads, with center drill mark, anodized aluminum</t>
+          <t>Alpha CN40-40B natural-convection pin-fin heatsink, Ø40 × 40 mm, black anodized</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LED carrier: board on front face, threads into condenser SMR1/M</t>
+          <t>LED module heatsink</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>Luxeon Star LEDs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SM1CP2M</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
+          <t>CN40-40B</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2939,24 +2962,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>§6.2</t>
+          <t>§6.3</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>One per LED module. Drill/tap, all through holes (§6.4): M2 board holes, M3 heatsink holes, lead pass-through holes at r = 11.0 mm.</t>
+          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LGT-018</t>
+          <t>LGT-019</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2965,89 +2988,92 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Alpha CN40-40B natural-convection pin-fin heatsink, Ø40 × 40 mm, black anodized</t>
+          <t>M3 × 0.5 × 6 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LED module heatsink</t>
+          <t>Heatsink-to-cap fasteners</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luxeon Star LEDs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CN40-40B</t>
-        </is>
+          <t>91292A111</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>§6.3</t>
+          <t>§§6.2, 6.4</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads.</t>
+          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LGT-019</t>
+          <t>SLT-001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Light source</t>
+          <t>Source slit</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M3 × 0.5 × 6 mm socket head screw, 18-8 SS</t>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heatsink-to-cap fasteners</t>
+          <t>Slit-head rotation mount; clamps the adapter spigot</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>91292A111</t>
+          <t>SM1RC/M</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3057,19 +3083,19 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>§§6.2, 6.4</t>
+          <t>§7.6</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw.</t>
+          <t>Second of the two in hand (CAR-002 holds the other).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLT-001</t>
+          <t>SLT-002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3078,16 +3104,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slit-head rotation mount; clamps the adapter spigot</t>
+          <t>Slit centering and slit-width adjusters</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3097,11 +3123,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SM1RC/M</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3115,19 +3141,19 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§§7.3–7.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Second of the two in hand (CAR-002 holds the other).</t>
+          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLT-002</t>
+          <t>SLT-003</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3140,7 +3166,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
+          <t>1/4 in-80 inserts</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3150,12 +3176,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FAS100</t>
+          <t>98625A950</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3178,14 +3204,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
+          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLT-003</t>
+          <t>SLT-004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3194,16 +3220,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1/4 in-80 inserts</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Slit centering and slit-width adjusters</t>
+          <t>Centering-stage preload, coaxial with the centering FAS100</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3213,15 +3239,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>98625A950</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3231,19 +3257,19 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>§§7.3–7.4</t>
+          <t>§7.3</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
+          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SLT-004</t>
+          <t>SLT-005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3252,30 +3278,30 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Centering-stage preload, coaxial with the centering FAS100</t>
+          <t>Hard bearing pads under the FAS100 ball tips</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3289,19 +3315,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>§7.3</t>
+          <t>§7.7</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
+          <t>Shared pack with CAR-012 and CAM-009.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLT-005</t>
+          <t>SLT-006</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3314,12 +3340,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hard bearing pads under the FAS100 ball tips</t>
+          <t>Slit blades (datum and movable)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3329,11 +3355,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>B000NNIIQM</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3347,19 +3373,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>§7.7</t>
+          <t>§7.1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Shared pack with CAR-012 and CAM-009.</t>
+          <t>Shared 100-pack with CAS-007: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLT-006</t>
+          <t>SLT-007</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3368,26 +3394,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Slit blades (datum and movable)</t>
+          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
+          <t>91292A114</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3405,19 +3431,19 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>§7.1</t>
+          <t>§§7.5–7.6</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Shared 100-pack with CAS-007.</t>
+          <t>Shared common 100-pack.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SLT-007</t>
+          <t>SLT-008</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3430,12 +3456,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
+          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3445,7 +3471,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3468,14 +3494,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Shared common 100-pack.</t>
+          <t>Shared common 100-pack (see CAS-004).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SLT-008</t>
+          <t>SLT-009</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3488,12 +3514,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
+          <t>Adapter spacer washers, two per adapter screw</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3503,7 +3529,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>93475A210</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3521,19 +3547,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>§§7.5–7.6</t>
+          <t>§7.6</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004).</t>
+          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SLT-009</t>
+          <t>SLT-010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3542,56 +3568,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Adapter spacer washers, two per adapter screw</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>93475A210</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>100</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed flexure slit head</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>§7.6</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
+          <t>§7.2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SLT-010</t>
+          <t>SLT-011</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3604,7 +3602,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PLA printed flexure slit head</t>
+          <t>PLA printed slit-head spigot adapter</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3614,14 +3612,14 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>§7.2</t>
+          <t>§7.6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SLT-011</t>
+          <t>SLT-012</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3630,11 +3628,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PLA printed slit-head spigot adapter</t>
+          <t>PLA printed slit-head blade clamp bars</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3644,44 +3642,72 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§7.5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SLT-012</t>
+          <t>CAR-002</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Source slit</t>
+          <t>Carriages</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Post attachment</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Thorlabs</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SM1RC/M</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>2</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PLA printed slit-head blade clamp bars</t>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>§7.5</t>
+          <t>§8.1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAR-001</t>
+          <t>CAR-005</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3689,14 +3715,17 @@
           <t>Carriages</t>
         </is>
       </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>Cassette positioner</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3706,11 +3735,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3722,16 +3751,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>§8.3</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAR-002</t>
+          <t>CAR-006</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3744,30 +3778,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Post attachment</t>
+          <t>Cassette counter-force plunger</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SM1RC/M</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3777,19 +3811,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>§8.1</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
+          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAR-005</t>
+          <t>CAR-007</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3802,7 +3836,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
+          <t>1/4 in-80 inserts</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3812,12 +3846,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FAS100</t>
+          <t>98625A950</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3840,14 +3874,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAR-006</t>
+          <t>CAR-009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3856,16 +3890,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>Brass escutcheon pins</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cassette counter-force plunger</t>
+          <t>Cassette interface datums</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3875,11 +3909,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>97936A109</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3893,19 +3927,19 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
+          <t>Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAR-007</t>
+          <t>CAR-010</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3918,52 +3952,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1/4 in-80 inserts</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Cassette positioner</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>98625A950</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>3</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>PLA printed carriage bodies</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
+          <t>Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAR-008</t>
+          <t>CAR-012</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3971,32 +3982,35 @@
           <t>Carriages</t>
         </is>
       </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Hard bearing pads for FAS100-driven plungers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4004,16 +4018,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>§8.3</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CAR-009</t>
+          <t>CAR-013</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4022,39 +4041,21 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Brass escutcheon pins</t>
+          <t>PLA printed open-center keeper frames</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cassette interface datums</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>97936A109</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>300</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4064,14 +4065,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cutoff carriage only.</t>
+          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAR-010</t>
+          <t>CAR-014</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4080,33 +4081,56 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PLA printed carriage bodies</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Keeper-frame fasteners (four end + four side)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>91292A114</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>100</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>§8.1</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cutoff carriage only.</t>
+          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAR-012</t>
+          <t>CAR-015</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4115,30 +4139,30 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hard bearing pads for FAS100-driven plungers</t>
+          <t>Keeper-frame captive nuts</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4152,37 +4176,32 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
+          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAR-013</t>
+          <t>CAS-001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PLA printed open-center keeper frames</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
+          <t>PLA printed cassettes</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4192,37 +4211,37 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.6</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
+          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CAR-014</t>
+          <t>CAS-002</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>Rubber/EPDM sheet</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Keeper-frame fasteners (four end + four side)</t>
+          <t>Retaining bar friction pads</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4232,15 +4251,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>9852N37</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4250,37 +4269,37 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§§7.5, 8.7</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
+          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAR-015</t>
+          <t>CAS-003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Keeper-frame captive nuts</t>
+          <t>Retaining bar screws</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4290,7 +4309,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>92125A133</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -4308,19 +4327,19 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
+          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAS-001</t>
+          <t>CAS-004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4329,33 +4348,56 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PLA printed cassettes</t>
+          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Retaining bar nuts</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>91828A211</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>100</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>§8.6</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
+          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAS-002</t>
+          <t>CAS-005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4364,16 +4406,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Rubber/EPDM sheet</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Retaining bar friction pads</t>
+          <t>Retaining bar washers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4383,15 +4425,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9852N37</t>
+          <t>93475A210</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4401,19 +4443,19 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>§§7.5, 8.7</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
+          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAS-003</t>
+          <t>CAS-007</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4422,26 +4464,26 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Retaining bar screws</t>
+          <t>Cutoff cassette</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>92125A133</t>
+          <t>B000NNIIQM</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -4459,19 +4501,19 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§8</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
+          <t>Shared 100-pack with SLT-006: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAS-004</t>
+          <t>CAS-008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4480,34 +4522,26 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
+          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Retaining bar nuts</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>91828A211</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>100</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>B0F29JW8CF</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4517,19 +4551,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§8.8</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAS-005</t>
+          <t>CAS-009</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4538,34 +4572,26 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
+          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Retaining bar washers</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>93475A210</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>100</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>B07P2HJJP6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4575,19 +4601,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§8.8</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAS-006</t>
+          <t>CAS-010</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4595,14 +4621,17 @@
           <t>Cassettes</t>
         </is>
       </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Existing stock; former slit-cassette allocation</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4612,15 +4641,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>100</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>B07GBMKMKY</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4628,16 +4649,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>§8.8</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No longer allocated after the flexure slit head decision (§7); the slit blades are SLT-006.</t>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAS-007</t>
+          <t>CAS-011</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4650,12 +4676,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cutoff cassette</t>
+          <t>Cutoff cassettes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4665,15 +4691,15 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
+          <t>B074V94RNR</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4683,19 +4709,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>§8</t>
+          <t>§8.9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CAS-008</t>
+          <t>CAM-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4703,22 +4729,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>B0F29JW8CF</t>
+          <t>iPhone 17</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4728,24 +4762,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>§8.8</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>§9.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAS-009</t>
+          <t>CAM-002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4753,22 +4782,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
+          <t>iPhone camera app</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Blackmagic Design</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>B07P2HJJP6</t>
+          <t>Blackmagic Camera</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4778,24 +4815,19 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>§8.8</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>§9.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAS-010</t>
+          <t>CAM-003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4803,22 +4835,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
+          <t>Telephoto lens, 17mm</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>iOgrapher</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>B07GBMKMKY</t>
+          <t>proSnap 7×</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4828,51 +4868,46 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>§8.8</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>§9.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAS-011</t>
+          <t>CAM-004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
+          <t>Ball-tip jack screws</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cutoff cassettes</t>
+          <t>Lens cradle adjusters</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>B074V94RNR</t>
+          <t>93339A252</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4886,14 +4921,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>§8.9</t>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAM-001</t>
+          <t>CAM-005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4902,34 +4942,34 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>M5 flanged heat-set inserts</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Lens cradle adjusters and yoke joints</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>iPhone 17</t>
+          <t>94459A797</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4939,14 +4979,19 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>§9.1</t>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CAM-002</t>
+          <t>CAM-006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4955,34 +5000,34 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>iPhone camera app</t>
+          <t>M5 thumb nuts, low profile black oxide</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Lens cradle adjuster handwheels</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackmagic Design</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Blackmagic Camera</t>
+          <t>92815A202</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4992,14 +5037,19 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>§9.1</t>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAM-003</t>
+          <t>CAM-007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5012,47 +5062,34 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Telephoto lens, 17mm</t>
+          <t>PLA printed phone rest</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Imager</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>iOgrapher</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>proSnap 7×</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>Roll support under the phone's lower edge</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>§9.2</t>
+          <t>§9.6</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Phone-specific rail shoe with an arm carrying the rest rod.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAM-004</t>
+          <t>CAM-008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5061,56 +5098,38 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ball-tip jack screws</t>
+          <t>PLA printed lens cradle shoe</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>93339A252</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>4</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>Rail-shoe saddle that carries the two yokes</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
+          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAM-005</t>
+          <t>CAM-009</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5119,30 +5138,30 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M5 flanged heat-set inserts</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters and yoke joints</t>
+          <t>Hard bearing pads under three lens-cradle screw tips</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>94459A797</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5156,19 +5175,19 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§§9.5–9.7</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
+          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAM-006</t>
+          <t>CAM-010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5177,16 +5196,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>M5 thumb nuts, low profile black oxide</t>
+          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lens cradle adjuster handwheels</t>
+          <t>Groove rods at the fourth lens-cradle screw</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5196,11 +5215,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>92815A202</t>
+          <t>91585A351</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5214,19 +5233,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§§9.5–9.7</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
+          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAM-007</t>
+          <t>CAM-011</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5235,38 +5254,38 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PLA printed phone rest</t>
+          <t>PLA printed lens collars</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roll support under the phone's lower edge</t>
+          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>§9.6</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Phone-specific rail shoe with an arm carrying the rest rod. Retainer and safety catch not yet designed.</t>
+          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAM-008</t>
+          <t>CAM-012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5275,21 +5294,39 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle shoe</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rail-shoe saddle that carries the two yokes</t>
+          <t>Lens collar clamp screws</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>91292A114</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>100</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5299,14 +5336,14 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
+          <t>Shared common 100-pack. One screw per collar.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CAM-009</t>
+          <t>CAM-013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5315,30 +5352,30 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hard bearing pads under three lens-cradle screw tips</t>
+          <t>Lens collar clamp nuts</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5352,19 +5389,19 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>§§9.5–9.7</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
+          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAM-010</t>
+          <t>CAM-014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5377,12 +5414,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
+          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Groove rods at the fourth lens-cradle screw</t>
+          <t>Lens cradle retaining bands</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5392,11 +5429,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>91585A351</t>
+          <t>9262K203</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5410,19 +5447,19 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>§§9.5–9.7</t>
+          <t>§9.8</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
+          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAM-011</t>
+          <t>CAM-015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5435,12 +5472,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PLA printed lens collars</t>
+          <t>PLA printed lens cradle yokes</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
+          <t>Carry the adjuster inserts and the retaining-band pegs</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5455,14 +5492,14 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
+          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAM-012</t>
+          <t>CAM-016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5475,12 +5512,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lens collar clamp screws</t>
+          <t>Yoke-to-shoe joint screws</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5490,7 +5527,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>92125A208</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -5508,19 +5545,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§§9.5, 9.7</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Shared common 100-pack. One screw per collar.</t>
+          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAM-013</t>
+          <t>CAM-017</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5529,16 +5566,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lens collar clamp nuts</t>
+          <t>Phone rest rod</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5548,11 +5585,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>91585A457</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5566,55 +5603,50 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.6</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
+          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CAM-014</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Lens cradle retaining bands</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>9262K203</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5624,24 +5656,19 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>§9.8</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CAM-015</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5649,70 +5676,83 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle yokes</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Carry the adjuster inserts and the retaining-band pegs</t>
+          <t>Base and adjuster plates</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>B09D941GXR</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>§9.5</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CAM-016</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yoke-to-shoe joint screws</t>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>92125A208</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5722,55 +5762,45 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>§§9.5, 9.7</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CAM-017</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Phone rest rod</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>91585A457</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5780,19 +5810,14 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>§9.6</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5801,25 +5826,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>B0B5RR41CT</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5833,14 +5858,14 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5849,34 +5874,29 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Base and adjuster plates</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5886,14 +5906,14 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5902,30 +5922,30 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mirror plate</t>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5939,14 +5959,14 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5959,25 +5979,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5987,14 +6007,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6003,29 +6023,34 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6035,14 +6060,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6051,25 +6076,30 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>3" Long Corner Bracket, aluminum</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6083,14 +6113,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6099,16 +6129,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spherical washers</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6118,15 +6148,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6136,14 +6166,19 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6152,11 +6187,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6166,11 +6206,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6184,14 +6224,19 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6200,16 +6245,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Spring seat washers</t>
+          <t>Quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6219,7 +6264,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -6237,14 +6282,19 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Four installed.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6253,30 +6303,30 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6290,14 +6340,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-011</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6305,14 +6360,17 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Mirror mounting</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6322,15 +6380,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>7587A25</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6340,19 +6398,14 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6361,16 +6414,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>Adhesive backed F1 felt</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Safety retainer padding</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6380,15 +6433,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>8334K15</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6398,19 +6451,19 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.8</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
+          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6419,56 +6472,28 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Adjuster plate to base plate mounting</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>96659A134</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>25</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed front safety retainers</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Eight installed, one under each bracket locknut.</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-015</t>
+          <t>MIR-026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6476,14 +6501,17 @@
           <t>Mirror cell</t>
         </is>
       </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Bracket screws, heads on the bracket</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6493,15 +6521,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>98164A527</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6509,31 +6537,34 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIR-017</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6543,15 +6574,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6559,31 +6590,29 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIR-018</t>
+          <t>SHP-002</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6593,15 +6622,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6609,102 +6638,95 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MIR-023</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Quick-release plate mounting screws</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6714,24 +6736,19 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>§10.9</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Four installed.</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6739,22 +6756,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -6772,24 +6789,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6797,12 +6814,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>LED mounting</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6812,7 +6829,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>2979N13</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -6830,19 +6847,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -6850,12 +6867,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Safety retainer padding</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6865,7 +6882,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8334K15</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -6873,7 +6890,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6883,82 +6900,108 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§§8.3, 8.4, 8.7, 10.4</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
+          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PLA printed front safety retainers</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Mirror mount releasing assembly surface</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>US Plastics</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MIR-022</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6968,37 +7011,32 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MIR-026</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bracket screws, heads on the bracket</t>
+          <t>PLA carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7008,15 +7046,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>98164A527</t>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7026,19 +7064,19 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
+          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7051,17 +7089,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
+          <t>White lithium grease, NLGI #2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>91458A160</t>
+          <t>Lucas Oil Products</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7079,14 +7117,19 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§10.4</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7099,7 +7142,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7109,7 +7157,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -7127,14 +7175,19 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§10.4</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7147,17 +7200,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -7171,13 +7229,23 @@
       <c r="J121" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>§10.3</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7190,22 +7258,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Source-slit blade spacing</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -7223,14 +7291,19 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>§7.4</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7243,12 +7316,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7258,7 +7331,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -7276,19 +7349,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7301,12 +7374,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7316,7 +7389,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -7334,14 +7407,19 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-007</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7349,14 +7427,35 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18 AWG wire</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fullcompass</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01001-1210</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7366,14 +7465,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§§8.6, 8.7</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-008</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7381,26 +7485,57 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Heat-shrink tubing</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>8305A32</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-009</t>
+          <t>SHP-025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7408,26 +7543,57 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>USB-C chargers/cables</t>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>DP100 power</t>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2979N15</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-010</t>
+          <t>SHP-026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7435,31 +7601,57 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thermal compound</t>
+          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LED heatsink interfaces</t>
+          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2979N14</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-027</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7472,12 +7664,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
+          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7487,7 +7679,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1818A45</t>
+          <t>8915N111</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -7505,19 +7697,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§§8.3, 8.4, 8.7, 10.4</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed); how it mates with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-028</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7530,22 +7722,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>Hakko FX888DX-10 soldering station</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>US Plastics</t>
+          <t>Heat-set insert installation (CAM-005)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>FX888DX-10</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7563,14 +7750,19 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-013</t>
+          <t>SHP-029</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7578,26 +7770,57 @@
           <t>Shop supplies</t>
         </is>
       </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Soldering tools / supplies</t>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LED wiring</t>
+          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>27445A201</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-030</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7610,22 +7833,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
+          <t>Backup hole spotter; spots the cap and heatsink holes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>B002IZFPQE</t>
+          <t>2915A11</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7643,46 +7866,48 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PLA carriage sliding-interface lubricant</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7694,48 +7919,45 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>§8.4</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>Existing stock; former carriage-tube allocation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>Thorlabs</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SM1L15</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7747,39 +7969,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>§10.4</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>UNU-003</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Existing stock; former spring guide / retract handle</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7789,11 +8003,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2890A56</t>
+          <t>91273A377</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -7805,39 +8019,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>§10.4</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>UNU-005</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7847,15 +8053,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7863,39 +8069,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>§10.3</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>UNU-006</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7905,11 +8103,11 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -7921,39 +8119,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>UNU-007</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7963,15 +8153,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7979,39 +8169,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>§§6.4, 10.9</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>UNU-008</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8021,15 +8203,15 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8037,53 +8219,45 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>§10.9</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>UNU-009</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8095,39 +8269,31 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>§§8.6, 8.7</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>UNU-010</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8137,15 +8303,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8153,363 +8319,15 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>SHP-025</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>2979N15</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SHP-026</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Lead holes through SM1CP2M cap and heatsink base</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>2979N14</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>To procure</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>SHP-027</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>8915N111</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>1</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>§9.7</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed); how it mates with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>SHP-028</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Hakko FX888DX-10 soldering station</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Heat-set insert installation (CAM-005)</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>FX888DX-10</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>1</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>§9.7</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>SHP-029</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>27445A201</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>1</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>SHP-030</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Backup hole spotter; spots the cap and heatsink holes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>2915A11</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>1</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L147"/>
-  <conditionalFormatting sqref="J2:J147">
+  <autoFilter ref="A1:L141"/>
+  <conditionalFormatting sqref="J2:J141">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -8526,8 +8344,13 @@
       <formula>"CAD open"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:L141">
+    <cfRule type="expression" priority="6" dxfId="5">
+      <formula>$B2&lt;&gt;$B1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J147" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J141" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -7089,7 +7089,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>White lithium grease, NLGI #2</t>
+          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7099,7 +7099,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lucas Oil Products</t>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>B009XE8M3G</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7112,7 +7117,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7122,7 +7127,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Existing shop stock inspected 2026-09-16 and appears usable.</t>
+          <t>Small tube to transport with the apparatus.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM'!$A$1:$L$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$L$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,10 +30,10 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="2">
@@ -474,387 +474,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iPhone Schlieren BOM / Procurement Tracker</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Canonical workbook</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Generated from bom/bom.csv in Git. Edits made here count only once reconciled into the CSV (reconcile-bom).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Design baseline</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>docs/design/ fragments in Git (consolidated: schlieren-design).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Quantity model</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Qty is the numeric required/allocated amount for that BOM line; package counts do not belong in Qty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Blank Qty</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Quantity is not yet frozen or the item is an as-required consumable/working-stock line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Package fields</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Package Size is units per Purchase Unit where known. Unknown vendor package sizes are intentionally blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Entry count</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>COUNTA(BOM!A:A)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Procurement state</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Entries</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Subsystem</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Entries</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="B11">
-        <f>COUNTIF(BOM!J:J,"In hand")</f>
-        <v/>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tabletop frame</t>
-        </is>
-      </c>
-      <c r="E11">
-        <f>COUNTIF(BOM!B:B,D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>On order</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>COUNTIF(BOM!J:J,"On order")</f>
-        <v/>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Optical supports</t>
-        </is>
-      </c>
-      <c r="E12">
-        <f>COUNTIF(BOM!B:B,D12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>To procure</t>
-        </is>
-      </c>
-      <c r="B13">
-        <f>COUNTIF(BOM!J:J,"To procure")</f>
-        <v/>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Light source</t>
-        </is>
-      </c>
-      <c r="E13">
-        <f>COUNTIF(BOM!B:B,D13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="B14">
-        <f>COUNTIF(BOM!J:J,"Specified")</f>
-        <v/>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Source slit</t>
-        </is>
-      </c>
-      <c r="E14">
-        <f>COUNTIF(BOM!B:B,D14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CAD ready</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>COUNTIF(BOM!J:J,"CAD ready")</f>
-        <v/>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Carriages</t>
-        </is>
-      </c>
-      <c r="E15">
-        <f>COUNTIF(BOM!B:B,D15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAD open</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>COUNTIF(BOM!J:J,"CAD open")</f>
-        <v/>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Cassettes</t>
-        </is>
-      </c>
-      <c r="E16">
-        <f>COUNTIF(BOM!B:B,D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Imager</t>
-        </is>
-      </c>
-      <c r="E17">
-        <f>COUNTIF(BOM!B:B,D17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mirror cell</t>
-        </is>
-      </c>
-      <c r="E18">
-        <f>COUNTIF(BOM!B:B,D18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="E19">
-        <f>COUNTIF(BOM!B:B,D19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Unused</t>
-        </is>
-      </c>
-      <c r="E20">
-        <f>COUNTIF(BOM!B:B,D20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rollup key</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Use Vendor + SKU for procurement rollups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Shared parts</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Keep separate BOM rows for separate subsystem allocations; roll them up by Vendor+SKU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Package math</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Vendor/SKU rollups may sum Qty and divide by Package Size where Package Size is known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Spare/surplus</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Unavoidable package surplus is not added to required Qty; track it in procurement/inventory rollups or notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data rule</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Do not insert subsystem header or separator rows inside the BOM table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Part defined by the design; vendor, SKU, or quantity still to be confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CAD ready</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Printed part with a build123d model in src/schlieren/parts/; ready to print and fit-test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CAD open</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Printed part whose custom geometry is still to be designed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -873,62 +492,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Subsystem</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pkg Size</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Purchase Unit</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Procurement state</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Source section</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6599,7 +6218,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHP-002</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6612,17 +6231,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -6636,18 +6255,13 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6660,7 +6274,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Metric feeler gauge set</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6670,7 +6289,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -6684,13 +6303,18 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6703,22 +6327,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Source-slit blade spacing</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -6736,14 +6360,19 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>§7.4</t>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6756,12 +6385,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>LED mounting</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6771,7 +6400,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>2979N13</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -6790,18 +6419,13 @@
       <c r="K113" t="inlineStr">
         <is>
           <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6814,12 +6438,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6829,7 +6453,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -6847,14 +6471,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§8.3, 8.4, 8.7, 10.4</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6867,22 +6496,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
+          <t>Mirror mount releasing assembly surface</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>US Plastics</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1818A45</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -6900,19 +6529,14 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>§§8.3, 8.4, 8.7, 10.4</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6925,22 +6549,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -6958,14 +6582,14 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6978,22 +6602,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
+          <t>PLA carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>B002IZFPQE</t>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -7011,14 +6635,19 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§8.4</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7031,22 +6660,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PLA carriage sliding-interface lubricant</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>B009XE8M3G</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -7059,24 +6688,24 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
+          <t>Small tube to transport with the apparatus.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7089,22 +6718,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>B009XE8M3G</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -7117,7 +6746,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7127,14 +6756,14 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Small tube to transport with the apparatus.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7147,12 +6776,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7162,7 +6791,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2890A56</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -7180,19 +6809,19 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7205,12 +6834,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7220,7 +6849,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -7238,19 +6867,19 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7263,12 +6892,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7278,7 +6907,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -7296,19 +6925,19 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7321,12 +6950,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7336,7 +6965,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -7354,19 +6983,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>§§6.4, 10.9</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7379,22 +7008,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Fullcompass</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>01001-1210</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -7402,7 +7031,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7412,19 +7041,19 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§8.6, 8.7</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7437,22 +7066,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>8305A32</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -7460,7 +7089,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7470,19 +7099,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>§§8.6, 8.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>SHP-025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7495,12 +7124,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7510,7 +7139,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>2979N15</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -7533,14 +7162,14 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-025</t>
+          <t>SHP-026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7553,12 +7182,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+          <t>Lead holes through SM1CP2M cap and heatsink base</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7568,7 +7197,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2979N15</t>
+          <t>2979N14</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -7581,7 +7210,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7591,14 +7220,14 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-026</t>
+          <t>SHP-027</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7611,12 +7240,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
+          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7626,7 +7255,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2979N14</t>
+          <t>8915N111</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -7639,24 +7268,24 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed). Replaces the 1/4 in plug tip UNU-011. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-027</t>
+          <t>SHP-028</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7669,22 +7298,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
+          <t>Hakko FX888DX-10 soldering station</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>McMaster</t>
+          <t>Heat-set insert installation (CAM-005)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8915N111</t>
+          <t>FX888DX-10</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -7707,14 +7331,14 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed); how it mates with SHP-002 is unverified. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
+          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-028</t>
+          <t>SHP-029</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7727,17 +7351,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Hakko FX888DX-10 soldering station</t>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Heat-set insert installation (CAM-005)</t>
+          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FX888DX-10</t>
+          <t>27445A201</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7755,19 +7384,19 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed); fit of SHP-002 unverified.</t>
+          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-029</t>
+          <t>SHP-030</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7780,12 +7409,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+          <t>Backup hole spotter; spots the cap and heatsink holes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7795,7 +7424,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>27445A201</t>
+          <t>2915A11</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7818,46 +7447,43 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
+          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-030</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Backup hole spotter; spots the cap and heatsink holes</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2915A11</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7869,21 +7495,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNU-001</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7893,26 +7514,26 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>Existing stock; former carriage-tube allocation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>SM1L15</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7926,14 +7547,14 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNU-002</t>
+          <t>UNU-003</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7943,22 +7564,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>Existing stock; former spring guide / retract handle</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>91273A377</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -7976,14 +7597,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNU-003</t>
+          <t>UNU-005</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7993,12 +7614,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8008,15 +7629,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8026,14 +7647,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNU-005</t>
+          <t>UNU-006</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8043,12 +7664,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8058,15 +7679,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8076,14 +7697,14 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNU-006</t>
+          <t>UNU-007</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8093,7 +7714,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8108,15 +7729,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8133,7 +7754,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNU-007</t>
+          <t>UNU-008</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8143,7 +7764,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8158,11 +7779,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -8183,7 +7804,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNU-008</t>
+          <t>UNU-009</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8193,12 +7814,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8208,11 +7829,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8226,14 +7847,14 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNU-009</t>
+          <t>UNU-010</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8243,12 +7864,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8258,11 +7879,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8276,14 +7897,14 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNU-010</t>
+          <t>UNU-011</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8293,12 +7914,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8308,15 +7924,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8326,7 +7942,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
         </is>
       </c>
     </row>
@@ -8361,4 +7977,385 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>iPhone Schlieren BOM / Procurement Tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Canonical workbook</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Generated from bom/bom.csv in Git. Edits made here count only once reconciled into the CSV (reconcile-bom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Design baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>docs/design/ fragments in Git (consolidated: schlieren-design).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quantity model</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Qty is the numeric required/allocated amount for that BOM line; package counts do not belong in Qty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blank Qty</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quantity is not yet frozen or the item is an as-required consumable/working-stock line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Package fields</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Package Size is units per Purchase Unit where known. Unknown vendor package sizes are intentionally blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Entry count</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTA(BOM!A:A)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Procurement state</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Subsystem</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(BOM!J:J,"In hand")</f>
+        <v/>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tabletop frame</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>COUNTIF(BOM!B:B,D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>On order</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>COUNTIF(BOM!J:J,"On order")</f>
+        <v/>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Optical supports</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>COUNTIF(BOM!B:B,D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(BOM!J:J,"To procure")</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Light source</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(BOM!B:B,D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTIF(BOM!J:J,"Specified")</f>
+        <v/>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Source slit</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(BOM!B:B,D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAD ready</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(BOM!J:J,"CAD ready")</f>
+        <v/>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Carriages</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(BOM!B:B,D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAD open</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(BOM!J:J,"CAD open")</f>
+        <v/>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cassettes</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(BOM!B:B,D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Imager</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>COUNTIF(BOM!B:B,D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mirror cell</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(BOM!B:B,D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(BOM!B:B,D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>COUNTIF(BOM!B:B,D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rollup key</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Use Vendor + SKU for procurement rollups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shared parts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Keep separate BOM rows for separate subsystem allocations; roll them up by Vendor+SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Package math</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vendor/SKU rollups may sum Qty and divide by Package Size where Package Size is known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Spare/surplus</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unavoidable package surplus is not added to required Qty; track it in procurement/inventory rollups or notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data rule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Do not insert subsystem header or separator rows inside the BOM table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Part defined by the design; vendor, SKU, or quantity still to be confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CAD ready</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Printed part with a build123d model in src/schlieren/parts/; ready to print and fit-test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CAD open</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Printed part whose custom geometry is still to be designed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.0 mm uncoated HSS short-length drill bit, 38 mm overall</t>
+          <t>2mm Premium High Speed Steel Jobber Length Drill, 10 pack</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7192,25 +7192,25 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2979N14</t>
+          <t>B07211L28S</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Same series as the 1.6 mm drill SHP-006. Deferred, not in the current order: lead hole size is provisional (§6.4), and the 2.5 mm drill SHP-025 may cut the lead holes instead. Decide after measuring the pigtail insulation.</t>
+          <t>Lead holes (§6.4): the pigtail wire measures about 1.7 mm over its insulation. McMaster alternative if wanted later: 2979N14, 2.0 mm uncoated HSS short-length drill bit, 38 mm overall (same series as the 1.6 mm drill SHP-006).</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$L$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$L$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2574,6 +2574,9 @@
           <t>CN40-40B</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>each</t>
@@ -2581,7 +2584,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2591,7 +2594,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads.</t>
+          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads. Three ordered and received; one spare.</t>
         </is>
       </c>
     </row>
@@ -2656,123 +2659,123 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SLT-001</t>
+          <t>LGT-020</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Source slit</t>
+          <t>Light source</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+          <t>M2 × 6 mm button head hex-drive screw 18-8 SS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Slit-head rotation mount; clamps the adapter spigot</t>
+          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SM1RC/M</t>
+          <t>92095A453</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Second of the two in hand (CAR-002 holds the other).</t>
+          <t>Longer alternative to LGT-011 (5 mm found a bit short).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLT-002</t>
+          <t>LGT-021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Source slit</t>
+          <t>Light source</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
+          <t>Nylon plastic washer for M2, 2.2 mm ID × 5.0 mm OD, off-white</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slit centering and slit-width adjusters</t>
+          <t>LED insulating washers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FAS100</t>
+          <t>95610A110</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>§§7.3–7.4</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
+          <t>Alternative to LGT-012.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLT-003</t>
+          <t>SLT-001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2781,31 +2784,31 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Slit-head rotation mount; clamps the adapter spigot</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Thorlabs</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SM1RC/M</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1/4 in-80 inserts</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Slit centering and slit-width adjusters</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>98625A950</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>each</t>
@@ -2818,19 +2821,19 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>§§7.3–7.4</t>
+          <t>§7.6</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
+          <t>Second of the two in hand (CAR-002 holds the other).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLT-004</t>
+          <t>SLT-002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2839,34 +2842,34 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Centering-stage preload, coaxial with the centering FAS100</t>
+          <t>Slit centering and slit-width adjusters</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2876,19 +2879,19 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>§7.3</t>
+          <t>§§7.3–7.4</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
+          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SLT-005</t>
+          <t>SLT-003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2901,30 +2904,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>1/4 in-80 inserts</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hard bearing pads under the FAS100 ball tips</t>
+          <t>Slit centering and slit-width adjusters</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>98625A950</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2934,19 +2937,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>§7.7</t>
+          <t>§§7.3–7.4</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Shared pack with CAR-012 and CAM-009.</t>
+          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLT-006</t>
+          <t>SLT-004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2955,30 +2958,30 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Slit blades (datum and movable)</t>
+          <t>Centering-stage preload, coaxial with the centering FAS100</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2992,19 +2995,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>§7.1</t>
+          <t>§7.3</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Shared 100-pack with CAS-007: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
+          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLT-007</t>
+          <t>SLT-005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3013,30 +3016,30 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
+          <t>Hard bearing pads under the FAS100 ball tips</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3050,19 +3053,19 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>§§7.5–7.6</t>
+          <t>§7.7</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Shared common 100-pack.</t>
+          <t>Shared pack with CAR-012 and CAM-009.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SLT-008</t>
+          <t>SLT-006</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3071,26 +3074,26 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
+          <t>Slit blades (datum and movable)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>B000NNIIQM</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3108,19 +3111,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>§§7.5–7.6</t>
+          <t>§7.1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004).</t>
+          <t>Shared 100-pack with CAS-007: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SLT-009</t>
+          <t>SLT-007</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3133,12 +3136,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Adapter spacer washers, two per adapter screw</t>
+          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3148,7 +3151,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>93475A210</t>
+          <t>91292A114</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3166,19 +3169,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§§7.5–7.6</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
+          <t>Shared common 100-pack.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SLT-010</t>
+          <t>SLT-008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3187,28 +3190,56 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PLA printed flexure slit head</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>91828A211</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>§7.2</t>
+          <t>§§7.5–7.6</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Shared common 100-pack (see CAS-004).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SLT-011</t>
+          <t>SLT-009</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3217,28 +3248,56 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PLA printed slit-head spigot adapter</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Adapter spacer washers, two per adapter screw</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>93475A210</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>100</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>§7.6</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SLT-012</t>
+          <t>SLT-010</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3247,11 +3306,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PLA printed slit-head blade clamp bars</t>
+          <t>PLA printed flexure slit head</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3261,19 +3320,19 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>§7.5</t>
+          <t>§7.2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAR-002</t>
+          <t>SLT-011</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Source slit</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3281,110 +3340,54 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Post attachment</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Thorlabs</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>SM1RC/M</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>PLA printed slit-head spigot adapter</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>§8.1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
+          <t>§7.6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAR-005</t>
+          <t>SLT-012</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Source slit</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Cassette positioner</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Thorlabs</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>FAS100</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>PLA printed slit-head blade clamp bars</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>§8.3</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
+          <t>§7.5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAR-006</t>
+          <t>CAR-002</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3397,30 +3400,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cassette counter-force plunger</t>
+          <t>Post attachment</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>SM1RC/M</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3430,19 +3433,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.1</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
+          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAR-007</t>
+          <t>CAR-005</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3455,7 +3458,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1/4 in-80 inserts</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3465,12 +3468,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>98625A950</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3493,14 +3496,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAR-009</t>
+          <t>CAR-006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3509,16 +3512,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Brass escutcheon pins</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cassette interface datums</t>
+          <t>Cassette counter-force plunger</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3528,11 +3531,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>97936A109</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3546,19 +3549,19 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cutoff carriage only.</t>
+          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAR-010</t>
+          <t>CAR-007</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3571,29 +3574,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PLA printed carriage bodies</t>
+          <t>1/4 in-80 inserts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cassette positioner</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>98625A950</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>§8.1</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cutoff carriage only.</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAR-012</t>
+          <t>CAR-009</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3602,30 +3628,30 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>Brass escutcheon pins</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hard bearing pads for FAS100-driven plungers</t>
+          <t>Cassette interface datums</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>97936A109</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3639,19 +3665,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
+          <t>Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CAR-013</t>
+          <t>CAR-010</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3664,12 +3690,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PLA printed open-center keeper frames</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
+          <t>PLA printed carriage bodies</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3679,19 +3700,19 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
+          <t>Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAR-014</t>
+          <t>CAR-012</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3700,30 +3721,30 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Keeper-frame fasteners (four end + four side)</t>
+          <t>Hard bearing pads for FAS100-driven plungers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3737,19 +3758,19 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
+          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAR-015</t>
+          <t>CAR-013</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3758,39 +3779,21 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>PLA printed open-center keeper frames</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Keeper-frame captive nuts</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>91828A211</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>100</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3800,67 +3803,90 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
+          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAS-001</t>
+          <t>CAR-014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Carriages</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PLA printed cassettes</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Keeper-frame fasteners (four end + four side)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>91292A114</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>100</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>§8.6</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
+          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CAS-002</t>
+          <t>CAR-015</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Carriages</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Rubber/EPDM sheet</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Retaining bar friction pads</t>
+          <t>Keeper-frame captive nuts</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3870,15 +3896,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9852N37</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3888,19 +3914,19 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>§§7.5, 8.7</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
+          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAS-003</t>
+          <t>CAS-001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3909,56 +3935,33 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Retaining bar screws</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>92125A133</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>100</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed cassettes</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§8.6</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
+          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAS-004</t>
+          <t>CAS-002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3967,16 +3970,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
+          <t>Rubber/EPDM sheet</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Retaining bar nuts</t>
+          <t>Retaining bar friction pads</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3986,15 +3989,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>9852N37</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4004,19 +4007,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§§7.5, 8.7</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
+          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAS-005</t>
+          <t>CAS-003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4029,12 +4032,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
+          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Retaining bar washers</t>
+          <t>Retaining bar screws</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4044,7 +4047,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>93475A210</t>
+          <t>92125A133</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -4067,14 +4070,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
+          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAS-007</t>
+          <t>CAS-004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4083,26 +4086,26 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cutoff cassette</t>
+          <t>Retaining bar nuts</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -4120,19 +4123,19 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>§8</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Shared 100-pack with SLT-006: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
+          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAS-008</t>
+          <t>CAS-005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4141,26 +4144,34 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Retaining bar washers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>B0F29JW8CF</t>
+          <t>93475A210</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>100</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4170,19 +4181,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>§8.8</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAS-009</t>
+          <t>CAS-007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4195,12 +4206,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Cutoff cassette</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4210,7 +4221,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B07P2HJJP6</t>
+          <t>B000NNIIQM</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>100</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4220,19 +4239,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>§8.8</t>
+          <t>§8</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>Shared 100-pack with SLT-006: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAS-010</t>
+          <t>CAS-008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4245,7 +4264,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
+          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4260,7 +4279,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>B07GBMKMKY</t>
+          <t>B0F29JW8CF</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4282,7 +4301,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAS-011</t>
+          <t>CAS-009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4295,12 +4314,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
+          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cutoff cassettes</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4310,15 +4329,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>B074V94RNR</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>B07P2HJJP6</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4328,19 +4339,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>§8.9</t>
+          <t>§8.8</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CAM-001</t>
+          <t>CAS-010</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4348,30 +4364,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>iPhone 17</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>B07GBMKMKY</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4381,19 +4389,24 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>§9.1</t>
+          <t>§8.8</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAM-002</t>
+          <t>CAS-011</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4401,22 +4414,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>iPhone camera app</t>
+          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Cutoff cassettes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blackmagic Design</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Blackmagic Camera</t>
+          <t>B074V94RNR</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -4434,14 +4447,14 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>§9.1</t>
+          <t>§8.9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAM-003</t>
+          <t>CAM-001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4454,7 +4467,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Telephoto lens, 17mm</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4464,12 +4477,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>iOgrapher</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>proSnap 7×</t>
+          <t>iPhone 17</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -4487,14 +4500,14 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>§9.2</t>
+          <t>§9.1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAM-004</t>
+          <t>CAM-002</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4503,30 +4516,30 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ball-tip jack screws</t>
+          <t>iPhone camera app</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Blackmagic Design</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>93339A252</t>
+          <t>Blackmagic Camera</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4540,19 +4553,14 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>§9.7</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
+          <t>§9.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAM-005</t>
+          <t>CAM-003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4561,34 +4569,34 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>M5 flanged heat-set inserts</t>
+          <t>Telephoto lens, 17mm</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters and yoke joints</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>iOgrapher</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>94459A797</t>
+          <t>proSnap 7×</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4598,19 +4606,14 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>§9.7</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
+          <t>§9.2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CAM-006</t>
+          <t>CAM-004</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4623,12 +4626,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>M5 thumb nuts, low profile black oxide</t>
+          <t>Ball-tip jack screws</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lens cradle adjuster handwheels</t>
+          <t>Lens cradle adjusters</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4638,15 +4641,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>92815A202</t>
+          <t>93339A252</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4661,14 +4664,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
+          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAM-007</t>
+          <t>CAM-005</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4677,38 +4680,56 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PLA printed phone rest</t>
+          <t>M5 flanged heat-set inserts</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roll support under the phone's lower edge</t>
+          <t>Lens cradle adjusters and yoke joints</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>94459A797</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>25</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>§9.6</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Phone-specific rail shoe with an arm carrying the rest rod.</t>
+          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAM-008</t>
+          <t>CAM-006</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4717,38 +4738,56 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle shoe</t>
+          <t>M5 thumb nuts, low profile black oxide</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rail-shoe saddle that carries the two yokes</t>
+          <t>Lens cradle adjuster handwheels</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>92815A202</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>10</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
+          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAM-009</t>
+          <t>CAM-007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4757,56 +4796,38 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>PLA printed phone rest</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hard bearing pads under three lens-cradle screw tips</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>B0DMCY4FN1</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>120</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Roll support under the phone's lower edge</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>§§9.5–9.7</t>
+          <t>§9.6</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
+          <t>Phone-specific rail shoe with an arm carrying the rest rod.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAM-010</t>
+          <t>CAM-008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4815,56 +4836,38 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
+          <t>PLA printed lens cradle shoe</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Groove rods at the fourth lens-cradle screw</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>91585A351</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>50</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Rail-shoe saddle that carries the two yokes</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>§§9.5–9.7</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
+          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAM-011</t>
+          <t>CAM-009</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4873,38 +4876,56 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PLA printed lens collars</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
+          <t>Hard bearing pads under three lens-cradle screw tips</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>B0DMCY4FN1</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>120</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§§9.5–9.7</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
+          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAM-012</t>
+          <t>CAM-010</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4917,12 +4938,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lens collar clamp screws</t>
+          <t>Groove rods at the fourth lens-cradle screw</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4932,11 +4953,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>91585A351</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4950,19 +4971,19 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§§9.5–9.7</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Shared common 100-pack. One screw per collar.</t>
+          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CAM-013</t>
+          <t>CAM-011</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4975,35 +4996,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>PLA printed lens collars</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lens collar clamp nuts</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>91828A211</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>100</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5013,14 +5016,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
+          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAM-014</t>
+          <t>CAM-012</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5033,12 +5036,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lens cradle retaining bands</t>
+          <t>Lens collar clamp screws</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5048,11 +5051,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>9262K203</t>
+          <t>91292A114</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5066,19 +5069,19 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>§9.8</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
+          <t>Shared common 100-pack. One screw per collar.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAM-015</t>
+          <t>CAM-013</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5091,17 +5094,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle yokes</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carry the adjuster inserts and the retaining-band pegs</t>
+          <t>Lens collar clamp nuts</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>91828A211</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>100</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5111,14 +5132,14 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
+          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAM-016</t>
+          <t>CAM-014</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5131,12 +5152,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
+          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Yoke-to-shoe joint screws</t>
+          <t>Lens cradle retaining bands</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5146,11 +5167,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>92125A208</t>
+          <t>9262K203</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5164,19 +5185,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>§§9.5, 9.7</t>
+          <t>§9.8</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
+          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAM-017</t>
+          <t>CAM-015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5185,87 +5206,74 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
+          <t>PLA printed lens cradle yokes</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Phone rest rod</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>91585A457</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>25</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Carry the adjuster inserts and the retaining-band pegs</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>§9.6</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
+          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>CAM-016</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
+          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yoke-to-shoe joint screws</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>B0B5RR41CT</t>
+          <t>92125A208</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5275,46 +5283,51 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§§9.5, 9.7</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>CAM-017</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Base and adjuster plates</t>
+          <t>Phone rest rod</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>91585A457</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5328,14 +5341,19 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§9.6</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5348,12 +5366,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Mirror plate</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5363,7 +5376,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -5381,14 +5394,14 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5397,29 +5410,34 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Base and adjuster plates</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>B09D941GXR</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5429,14 +5447,14 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5445,25 +5463,30 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5477,14 +5500,14 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5497,7 +5520,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5507,7 +5530,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -5532,7 +5555,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5545,22 +5568,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Spherical washers</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -5578,14 +5596,14 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5598,25 +5616,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5626,14 +5644,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5642,16 +5660,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spring seat washers</t>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5661,15 +5679,15 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5679,14 +5697,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5695,16 +5713,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5714,15 +5727,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5732,14 +5745,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5748,16 +5761,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5767,11 +5780,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5785,19 +5798,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5806,11 +5814,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+          <t>3" Long Corner Bracket, aluminum</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5825,15 +5833,15 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>96659A134</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5844,18 +5852,13 @@
       <c r="K102" t="inlineStr">
         <is>
           <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5864,16 +5867,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Quick-release plate mounting screws</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5883,11 +5886,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5901,19 +5904,19 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.7</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Four installed.</t>
+          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5922,34 +5925,34 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5959,19 +5962,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.7</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
+          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5980,16 +5983,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>Quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5999,15 +6002,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6017,14 +6020,19 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.9</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Four installed.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6037,22 +6045,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Safety retainer padding</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8334K15</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -6060,7 +6068,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6070,19 +6078,19 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6091,28 +6099,51 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PLA printed front safety retainers</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Mirror mounting</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>7587A25</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-026</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6121,16 +6152,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+          <t>Adhesive backed F1 felt</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bracket screws, heads on the bracket</t>
+          <t>Safety retainer padding</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6140,15 +6171,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>98164A527</t>
+          <t>8334K15</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6158,110 +6189,107 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.8</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
+          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>91458A160</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>1</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>PLA printed front safety retainers</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§10.8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>MIR-026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Bracket screws, heads on the bracket</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>98164A527</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6274,22 +6302,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Source-slit blade spacing</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -6307,14 +6330,14 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>§7.4</t>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6327,22 +6350,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M2 tap</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -6356,23 +6374,13 @@
       <c r="J112" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6385,22 +6393,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>Metric feeler gauge set</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -6418,14 +6426,14 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6438,12 +6446,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6453,7 +6461,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1818A45</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -6471,19 +6479,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>§§8.3, 8.4, 8.7, 10.4</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6496,22 +6504,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>LED mounting</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>2979N13</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -6529,14 +6537,14 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§6.4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6549,22 +6557,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>B002IZFPQE</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -6582,14 +6590,19 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§§8.3, 8.4, 8.7, 10.4</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6602,22 +6615,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PLA carriage sliding-interface lubricant</t>
+          <t>Mirror mount releasing assembly surface</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>US Plastics</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -6635,19 +6648,14 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>§8.4</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6660,12 +6668,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6675,7 +6683,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>B009XE8M3G</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -6688,24 +6696,19 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§10.4</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Small tube to transport with the apparatus.</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6718,12 +6721,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>PLA carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6733,7 +6736,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2890A56</t>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -6751,19 +6754,19 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6776,22 +6779,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>B009XE8M3G</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -6809,19 +6812,19 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Small tube to transport with the apparatus.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6834,12 +6837,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6849,7 +6852,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -6867,19 +6870,19 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6892,12 +6895,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6907,7 +6910,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -6925,19 +6928,19 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>§§6.4, 10.9</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6950,12 +6953,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6965,7 +6968,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -6988,14 +6991,14 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7008,22 +7011,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -7031,7 +7034,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7041,19 +7044,19 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§§8.6, 8.7</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7066,12 +7069,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7081,7 +7084,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -7099,19 +7102,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
+          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-025</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7124,22 +7127,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Fullcompass</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2979N15</t>
+          <t>01001-1210</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -7147,7 +7150,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7157,19 +7160,19 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§8.6, 8.7</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-026</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7182,35 +7185,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2mm Premium High Speed Steel Jobber Length Drill, 10 pack</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>B07211L28S</t>
+          <t>8305A32</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7220,14 +7223,14 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Lead holes (§6.4): the pigtail wire measures about 1.7 mm over its insulation. McMaster alternative if wanted later: 2979N14, 2.0 mm uncoated HSS short-length drill bit, 38 mm overall (same series as the 1.6 mm drill SHP-006).</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-027</t>
+          <t>SHP-025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7240,12 +7243,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7255,7 +7258,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8915N111</t>
+          <t>2979N15</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -7273,19 +7276,19 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed). Replaces the 1/4 in plug tip UNU-011. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-028</t>
+          <t>SHP-026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7298,47 +7301,52 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Hakko FX888DX-10 soldering station</t>
+          <t>2mm Premium High Speed Steel Jobber Length Drill, 10 pack</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heat-set insert installation (CAM-005)</t>
+          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FX888DX-10</t>
+          <t>B07211L28S</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed).</t>
+          <t>Lead holes (§6.4): the pigtail wire measures about 1.7 mm over its insulation. McMaster alternative if wanted later: 2979N14, 2.0 mm uncoated HSS short-length drill bit, 38 mm overall (same series as the 1.6 mm drill SHP-006).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-029</t>
+          <t>SHP-027</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7351,12 +7359,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7366,7 +7374,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>27445A201</t>
+          <t>8915N111</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7384,19 +7392,19 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed). Replaces the 1/4 in plug tip UNU-011. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-030</t>
+          <t>SHP-028</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7409,22 +7417,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
+          <t>Hakko FX888DX-10 soldering station</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Backup hole spotter; spots the cap and heatsink holes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>McMaster</t>
+          <t>Heat-set insert installation (CAM-005)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2915A11</t>
+          <t>FX888DX-10</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7442,48 +7445,51 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNU-001</t>
+          <t>SHP-029</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>27445A201</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7495,45 +7501,53 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNU-002</t>
+          <t>SHP-030</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>Backup hole spotter; spots the cap and heatsink holes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>2915A11</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7545,16 +7559,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>§6.4</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNU-003</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7564,26 +7583,26 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7597,14 +7616,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNU-005</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7614,30 +7633,30 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Existing stock; former carriage-tube allocation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>SM1L15</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7647,14 +7666,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNU-006</t>
+          <t>UNU-003</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7664,12 +7683,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing stock; former spring guide / retract handle</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7679,11 +7698,11 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>91273A377</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -7697,14 +7716,14 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNU-007</t>
+          <t>UNU-005</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7714,12 +7733,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7729,7 +7748,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -7747,14 +7766,14 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNU-008</t>
+          <t>UNU-006</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7764,7 +7783,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7779,15 +7798,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7804,7 +7823,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNU-009</t>
+          <t>UNU-007</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7814,12 +7833,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7829,7 +7848,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -7847,14 +7866,14 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNU-010</t>
+          <t>UNU-008</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7864,12 +7883,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7879,11 +7898,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -7897,58 +7916,158 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>UNU-009</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Existing alternate bracket screw stock</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>90585A997</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>5</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>UNU-010</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>92125A194</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>100</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>UNU-011</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Unused</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Heat-set installation tip</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>McMaster</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>92160A327</t>
         </is>
       </c>
-      <c r="H141" t="n">
-        <v>1</v>
-      </c>
-      <c r="I141" t="inlineStr">
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>each</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L141"/>
-  <conditionalFormatting sqref="J2:J141">
+  <autoFilter ref="A1:L143"/>
+  <conditionalFormatting sqref="J2:J143">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -7965,13 +8084,13 @@
       <formula>"CAD open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:L141">
+  <conditionalFormatting sqref="A2:L143">
     <cfRule type="expression" priority="6" dxfId="5">
       <formula>$B2&lt;&gt;$B1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J141" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J143" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hard bearing pads under the FAS100 ball tips</t>
+          <t>Flat bearing inserts under the FAS100 ball tips</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hard bearing pads for FAS100-driven plungers</t>
+          <t>Flat bearing inserts for FAS100-driven plungers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets; one hard contact insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
+          <t>Nickel-plated rectangular magnets; one flat bearing insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-slot clamp holes.</t>
+          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-channel clamp holes.</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hard bearing pads under three lens-cradle screw tips</t>
+          <t>Flat bearing inserts under three lens-cradle screw tips</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a magnet.</t>
+          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a flat bearing insert.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>§5.3</t>
+          <t>§5.2</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>§5.3</t>
+          <t>§5.2</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>§5.3</t>
+          <t>§5.2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>§5.3</t>
+          <t>§5.2</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LGT-011</t>
+          <t>LGT-012</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
+          <t>M2 nylon washers</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
+          <t>LED insulating washers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2198,11 +2198,8 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>92095A452</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>25</v>
+          <t>91545A410</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2223,7 +2220,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LGT-012</t>
+          <t>LGT-013</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2232,31 +2229,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M2 nylon washers</t>
+          <t>ALIENTEK DP100 DC Power Supply Variable, 30V 5A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LED insulating washers</t>
+          <t>LED CC/CV power supply</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>91545A410</t>
-        </is>
+          <t>B0CWRG6YFM</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2266,14 +2266,14 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§6.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LGT-013</t>
+          <t>LGT-014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2282,30 +2282,30 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ALIENTEK DP100 DC Power Supply Variable, 30V 5A</t>
+          <t>Cable Assembly, Micro-Fit 3.0 P-S 2ckt 150 mm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LED CC/CV power supply</t>
+          <t>LED pigtails</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Mouser</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B0CWRG6YFM</t>
+          <t>538-214758-1021</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LGT-014</t>
+          <t>LGT-015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cable Assembly, Micro-Fit 3.0 P-S 2ckt 150 mm</t>
+          <t>Cable Assembly, Micro-Fit 3.0 R-S 2ckt 600MM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LED pigtails</t>
+          <t>Power supply pigtail</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>538-214758-1021</t>
+          <t>538-214756-1023</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2379,7 +2379,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LGT-015</t>
+          <t>LGT-016</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cable Assembly, Micro-Fit 3.0 R-S 2ckt 600MM</t>
+          <t>Banana plug set 1 blk 1 red</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Power supply pigtail</t>
+          <t>DP100 connection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2407,11 +2407,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>538-214756-1023</t>
+          <t>565-1825-02</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LGT-016</t>
+          <t>LGT-017</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2441,26 +2441,26 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Banana plug set 1 blk 1 red</t>
+          <t>SM1 end cap, external threads, with center drill mark, anodized aluminum</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DP100 connection</t>
+          <t>LED carrier: board on front face, threads into condenser SMR1/M</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mouser</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>565-1825-02</t>
+          <t>SM1CP2M</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2478,14 +2478,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>§6.5</t>
+          <t>§6.2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>One per LED module. Drill/tap, all through holes (§6.4): M2 board holes, M3 heatsink holes, lead pass-through holes at r = 11.0 mm.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LGT-017</t>
+          <t>LGT-018</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2498,26 +2503,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SM1 end cap, external threads, with center drill mark, anodized aluminum</t>
+          <t>Alpha CN40-40B natural-convection pin-fin heatsink, Ø40 × 40 mm, black anodized</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LED carrier: board on front face, threads into condenser SMR1/M</t>
+          <t>LED module heatsink</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>Luxeon Star LEDs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SM1CP2M</t>
+          <t>CN40-40B</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2531,19 +2536,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>§6.2</t>
+          <t>§6.3</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>One per LED module. Drill/tap, all through holes (§6.4): M2 board holes, M3 heatsink holes, lead pass-through holes at r = 11.0 mm.</t>
+          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads. Three ordered and received; one spare.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LGT-018</t>
+          <t>LGT-019</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2552,34 +2557,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Alpha CN40-40B natural-convection pin-fin heatsink, Ø40 × 40 mm, black anodized</t>
+          <t>M3 × 0.5 × 6 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LED module heatsink</t>
+          <t>Heatsink-to-cap fasteners</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luxeon Star LEDs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CN40-40B</t>
+          <t>91292A111</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2589,19 +2594,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>§6.3</t>
+          <t>§§6.2, 6.4</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>One per LED module; bolted to SM1CP2M rear. Drill base for M3 screws in open pin cells and for leads. Three ordered and received; one spare.</t>
+          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LGT-019</t>
+          <t>LGT-020</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2610,16 +2615,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M3 × 0.5 × 6 mm socket head screw, 18-8 SS</t>
+          <t>M2 × 6 mm button head hex-drive screw 18-8 SS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heatsink-to-cap fasteners</t>
+          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2629,11 +2634,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>91292A111</t>
+          <t>92095A453</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2647,19 +2652,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>§§6.2, 6.4</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Three per module. Provisional length (3 mm base + ~3 mm thread into the through-tapped cap; shorter than the cap thickness). Same series as the common 12 mm screw.</t>
+          <t>6 mm length fits better than the 5 mm screw UNU-012.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LGT-020</t>
+          <t>LGT-021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2672,12 +2677,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M2 × 6 mm button head hex-drive screw 18-8 SS</t>
+          <t>Nylon plastic washer for M2, 2.2 mm ID × 5.0 mm OD, off-white</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LED board mounting screws, tapped into SM1CP2M cap</t>
+          <t>LED insulating washers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2687,11 +2692,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>92095A453</t>
+          <t>95610A110</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2710,72 +2715,72 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Longer alternative to LGT-011 (5 mm found a bit short).</t>
+          <t>Alternative to LGT-012.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LGT-021</t>
+          <t>SLT-001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Light source</t>
+          <t>Source slit</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nylon plastic washer for M2, 2.2 mm ID × 5.0 mm OD, off-white</t>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LED insulating washers</t>
+          <t>Slit-head rotation mount; clamps the adapter spigot</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>95610A110</t>
+          <t>SM1RC/M</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§7.6</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Alternative to LGT-012.</t>
+          <t>Second of the two in hand (CAR-002 holds the other).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLT-001</t>
+          <t>SLT-002</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2784,16 +2789,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Slit-head rotation mount; clamps the adapter spigot</t>
+          <t>Slit centering and slit-width adjusters</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2803,11 +2808,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SM1RC/M</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2821,19 +2826,19 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§§7.3–7.4</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Second of the two in hand (CAR-002 holds the other).</t>
+          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLT-002</t>
+          <t>SLT-003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2846,7 +2851,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
+          <t>1/4 in-80 inserts</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2856,12 +2861,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FAS100</t>
+          <t>98625A950</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2884,14 +2889,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-005: three in hand, two here, one in the cutoff carriage; no spare.</t>
+          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SLT-003</t>
+          <t>SLT-004</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2900,16 +2905,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1/4 in-80 inserts</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slit centering and slit-width adjusters</t>
+          <t>Centering-stage preload, coaxial with the centering FAS100</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2919,15 +2924,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>98625A950</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2937,19 +2942,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>§§7.3–7.4</t>
+          <t>§7.3</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Shared stock with CAR-007: three in hand, two here, one in the cutoff carriage; no spare. Finish printed bores with a 5/16 in drill; a light hand ream gave a good press fit on the first print.</t>
+          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLT-004</t>
+          <t>SLT-005</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2958,30 +2963,30 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Centering-stage preload, coaxial with the centering FAS100</t>
+          <t>Flat bearing inserts under the FAS100 ball tips</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>B0DMCY4FN1</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2995,19 +3000,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>§7.3</t>
+          <t>§7.7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Measured OD 0.272 in / 6.91 mm. Installed fully compressed by hand (§7.3). Shared 5-pack with CAR-006.</t>
+          <t>Shared pack with CAR-012 and CAM-009.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLT-005</t>
+          <t>SLT-006</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3020,12 +3025,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flat bearing inserts under the FAS100 ball tips</t>
+          <t>Slit blades (datum and movable)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3035,11 +3040,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>B000NNIIQM</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3053,19 +3058,19 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>§7.7</t>
+          <t>§7.1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Shared pack with CAR-012 and CAM-009.</t>
+          <t>Shared 100-pack with CAS-007: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SLT-006</t>
+          <t>SLT-007</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3074,26 +3079,26 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slit blades (datum and movable)</t>
+          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
+          <t>91292A114</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3111,19 +3116,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>§7.1</t>
+          <t>§§7.5–7.6</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Shared 100-pack with CAS-007: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
+          <t>Shared common 100-pack.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SLT-007</t>
+          <t>SLT-008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3136,12 +3141,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blade clamp bars (4) and adapter-to-head (4)</t>
+          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3151,7 +3156,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3174,14 +3179,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Shared common 100-pack.</t>
+          <t>Shared common 100-pack (see CAS-004).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SLT-008</t>
+          <t>SLT-009</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3194,12 +3199,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Captive nuts for blade clamp bars (4) and adapter (4)</t>
+          <t>Adapter spacer washers, two per adapter screw</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3209,7 +3214,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>93475A210</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3227,19 +3232,19 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>§§7.5–7.6</t>
+          <t>§7.6</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004).</t>
+          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SLT-009</t>
+          <t>SLT-010</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3248,56 +3253,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Adapter spacer washers, two per adapter screw</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>93475A210</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>100</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed flexure slit head</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>§7.6</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Two stacked per screw set the ~1 mm adapter standoff. Shared 100-pack with CAS-005.</t>
+          <t>§7.2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SLT-010</t>
+          <t>SLT-011</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3310,7 +3287,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PLA printed flexure slit head</t>
+          <t>PLA printed slit-head spigot adapter</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3320,14 +3297,14 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>§7.2</t>
+          <t>§7.6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SLT-011</t>
+          <t>SLT-012</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3336,11 +3313,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PLA printed slit-head spigot adapter</t>
+          <t>PLA printed slit-head blade clamp bars</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3350,44 +3327,72 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>§7.6</t>
+          <t>§7.5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLT-012</t>
+          <t>CAR-002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Source slit</t>
+          <t>Carriages</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Post attachment</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Thorlabs</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SM1RC/M</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PLA printed slit-head blade clamp bars</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>§7.5</t>
+          <t>§8.1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAR-002</t>
+          <t>CAR-005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3400,12 +3405,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Slip ring for SM1 lens tubes, M4 Tap</t>
+          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Post attachment</t>
+          <t>Cassette positioner</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3415,11 +3420,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SM1RC/M</t>
+          <t>FAS100</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3433,19 +3438,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>§8.1</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cutoff carriage. The second in-hand ring is allocated to the slit head (SLT-001).</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAR-005</t>
+          <t>CAR-006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3458,30 +3463,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fine adjustment screw with knob, 1/4"-80, 1.00" long</t>
+          <t>Compression springs</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cassette positioner</t>
+          <t>Cassette counter-force plunger</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FAS100</t>
+          <t>2006N292</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3496,14 +3501,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-002); no spare.</t>
+          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAR-006</t>
+          <t>CAR-007</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3516,12 +3521,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Compression springs</t>
+          <t>1/4 in-80 inserts</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cassette counter-force plunger</t>
+          <t>Cassette positioner</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3531,15 +3536,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2006N292</t>
+          <t>98625A950</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3554,14 +3559,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Shared 5-pack with the slit-head preload spring (SLT-004).</t>
+          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAR-007</t>
+          <t>CAR-009</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3570,16 +3575,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1/4 in-80 inserts</t>
+          <t>Brass escutcheon pins</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cassette positioner</t>
+          <t>Cassette interface datums</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3589,15 +3594,15 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>98625A950</t>
+          <t>97936A109</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3607,19 +3612,19 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Three in hand: one for the cutoff carriage, two for the slit head (SLT-003); no spare.</t>
+          <t>Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAR-009</t>
+          <t>CAR-010</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3628,44 +3633,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Brass escutcheon pins</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Cassette interface datums</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>97936A109</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>300</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed carriage bodies</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.1</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3677,7 +3659,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CAR-010</t>
+          <t>CAR-012</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3690,29 +3672,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PLA printed carriage bodies</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Flat bearing inserts for FAS100-driven plungers</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>B0DMCY4FN1</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>120</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>§8.1</t>
+          <t>§8.3</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cutoff carriage only.</t>
+          <t>Nickel-plated rectangular magnets; one flat bearing insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAR-012</t>
+          <t>CAR-013</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3725,52 +3730,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>PLA printed open-center keeper frames</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Flat bearing inserts for FAS100-driven plungers</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>B0DMCY4FN1</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>120</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>§8.3</t>
+          <t>§8.4</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets; one flat bearing insert for the FAS100-driven PLA plunger of the cutoff carriage.</t>
+          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAR-013</t>
+          <t>CAR-014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3779,21 +3766,39 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PLA printed open-center keeper frames</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Retain plunger guide ears while leaving cassette-loading aperture open</t>
+          <t>Keeper-frame fasteners (four end + four side)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>91292A114</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>100</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3803,14 +3808,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Perimeter frame; eight M3 screws (four end, four side in lugs); 3.0 mm side members, with a 5 mm-side-member fallback keeper if lift is excessive; carries the end-wall spring-cup roof (§8.5). Cutoff carriage only.</t>
+          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAR-014</t>
+          <t>CAR-015</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3823,12 +3828,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Keeper-frame fasteners (four end + four side)</t>
+          <t>Keeper-frame captive nuts</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3838,7 +3843,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3861,72 +3866,49 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Reuse common M3 × 12 mm stock. Heads bear directly on PLA in ~0.5 mm recesses; tighten only to a light snug.</t>
+          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CAR-015</t>
+          <t>CAS-001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carriages</t>
+          <t>Cassettes</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Keeper-frame captive nuts</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>91828A211</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>100</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>PLA printed cassettes</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§8.6</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Full-height DIN 934 nut. ~2.5 mm captive hex pocket from carriage back, leaving ~1.5 mm PLA floor above pocket.</t>
+          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAS-001</t>
+          <t>CAS-002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3935,33 +3917,56 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PLA printed cassettes</t>
+          <t>Rubber/EPDM sheet</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Retaining bar friction pads</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>9852N37</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>§8.6</t>
+          <t>§§7.5, 8.7</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Cutoff cassettes; each takes four clamp-bar screws, nuts, and washers (CAS-003 to CAS-005).</t>
+          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAS-002</t>
+          <t>CAS-003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3970,16 +3975,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Rubber/EPDM sheet</t>
+          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Retaining bar friction pads</t>
+          <t>Retaining bar screws</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3989,15 +3994,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9852N37</t>
+          <t>92125A133</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4007,19 +4012,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>§§7.5, 8.7</t>
+          <t>§8.7</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
+          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAS-003</t>
+          <t>CAS-004</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4032,12 +4037,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M3 × 14 mm 90° flat-head socket screw, 18-8 SS</t>
+          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Retaining bar screws</t>
+          <t>Retaining bar nuts</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4047,7 +4052,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>92125A133</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -4070,14 +4075,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Fit-tested on built cassettes with 4 mm bars: full nut engagement, head flush in countersink.</t>
+          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAS-004</t>
+          <t>CAS-005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4090,12 +4095,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M3 × 0.5 full-height hex nut, 18-8 SS</t>
+          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Retaining bar nuts</t>
+          <t>Retaining bar washers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4105,7 +4110,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>93475A210</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -4128,14 +4133,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Shared 100-pack: 33 total nuts now allocated across split clamps, keeper frames, cassette retaining bars, the slit head, and the lens collars; 67 spare.</t>
+          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAS-005</t>
+          <t>CAS-007</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4144,26 +4149,26 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>M3 flat washer, 3.2 mm ID × 7 mm OD, 18-8 SS</t>
+          <t>Razor blade, Stanley 11-515</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Retaining bar washers</t>
+          <t>Cutoff cassette</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>93475A210</t>
+          <t>B000NNIIQM</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -4181,19 +4186,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>§8.7</t>
+          <t>§8</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Under exposed nut, on printed retaining bar. Shared 100-pack with the slit-head spacer washers (SLT-009).</t>
+          <t>Shared 100-pack with SLT-006: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAS-007</t>
+          <t>CAS-008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4206,12 +4211,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Razor blade, Stanley 11-515</t>
+          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cutoff cassette</t>
+          <t>Dark-field cutoff filament</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4221,15 +4226,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B000NNIIQM</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>100</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>B0F29JW8CF</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4239,19 +4236,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>§8</t>
+          <t>§8.8</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Shared 100-pack with SLT-006: three blades allocated (two in the slit head, one in a cutoff cassette); 97 spare.</t>
+          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAS-008</t>
+          <t>CAS-009</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4264,7 +4261,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Magnet wire, 44 AWG (~0.0508 mm bare conductor)</t>
+          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4279,7 +4276,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>B0F29JW8CF</t>
+          <t>B07P2HJJP6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4301,7 +4298,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAS-009</t>
+          <t>CAS-010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4314,7 +4311,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Magnet wire, 34 AWG (~0.160 mm bare conductor)</t>
+          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4329,7 +4326,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>B07P2HJJP6</t>
+          <t>B07GBMKMKY</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4351,7 +4348,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CAS-010</t>
+          <t>CAS-011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4364,12 +4361,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Magnet wire, 30 AWG (~0.255 mm bare conductor)</t>
+          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dark-field cutoff filament</t>
+          <t>Cutoff cassettes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4379,7 +4376,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>B07GBMKMKY</t>
+          <t>B074V94RNR</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>each</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4389,24 +4394,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>§8.8</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Enamel-coated copper. Finished outside diameter will be slightly larger than the nominal bare-conductor diameter.</t>
+          <t>§8.9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAS-011</t>
+          <t>CAM-001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Rosco Roscolux Designer Color Selector Swatchbook - 3 x 6</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cutoff cassettes</t>
+          <t>Imager</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>B074V94RNR</t>
+          <t>iPhone 17</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>§8.9</t>
+          <t>§9.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAM-001</t>
+          <t>CAM-002</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>iPhone camera app</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Blackmagic Design</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>iPhone 17</t>
+          <t>Blackmagic Camera</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -4507,7 +4507,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAM-002</t>
+          <t>CAM-003</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>iPhone camera app</t>
+          <t>Telephoto lens, 17mm</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackmagic Design</t>
+          <t>iOgrapher</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Blackmagic Camera</t>
+          <t>proSnap 7×</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>§9.1</t>
+          <t>§9.2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAM-003</t>
+          <t>CAM-004</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4569,30 +4569,30 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Telephoto lens, 17mm</t>
+          <t>Ball-tip jack screws</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Lens cradle adjusters</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>iOgrapher</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>proSnap 7×</t>
+          <t>93339A252</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4606,14 +4606,19 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>§9.2</t>
+          <t>§9.7</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CAM-004</t>
+          <t>CAM-005</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4622,16 +4627,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ball-tip jack screws</t>
+          <t>M5 flanged heat-set inserts</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters</t>
+          <t>Lens cradle adjusters and yoke joints</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4641,15 +4646,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>93339A252</t>
+          <t>94459A797</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4664,14 +4669,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Two under each lens collar. All four of the pack in hand are allocated; no spare.</t>
+          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAM-005</t>
+          <t>CAM-006</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4680,16 +4685,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>M5 flanged heat-set inserts</t>
+          <t>M5 thumb nuts, low profile black oxide</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lens cradle adjusters and yoke joints</t>
+          <t>Lens cradle adjuster handwheels</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4699,11 +4704,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>94459A797</t>
+          <t>92815A202</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4722,14 +4727,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Four set in the yoke arms (one per adjuster) and two in the yoke column feet for the joint screws (CAM-016). One pack of 25 in hand; 19 spare.</t>
+          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAM-006</t>
+          <t>CAM-007</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4738,56 +4743,38 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M5 thumb nuts, low profile black oxide</t>
+          <t>PLA printed phone rest</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lens cradle adjuster handwheels</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>92815A202</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>10</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Roll support under the phone's lower edge</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§9.6</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Threadlocked mid-screw. Shared 10-pack with the yaw clamp thumb nuts (FRM-010).</t>
+          <t>Phone-specific rail shoe with an arm carrying the rest rod.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAM-007</t>
+          <t>CAM-008</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4800,12 +4787,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PLA printed phone rest</t>
+          <t>PLA printed lens cradle shoe</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roll support under the phone's lower edge</t>
+          <t>Rail-shoe saddle that carries the two yokes</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4815,19 +4802,19 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>§9.6</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Phone-specific rail shoe with an arm carrying the rest rod.</t>
+          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-channel clamp holes.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAM-008</t>
+          <t>CAM-009</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4836,38 +4823,56 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle shoe</t>
+          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rail-shoe saddle that carries the two yokes</t>
+          <t>Flat bearing inserts under three lens-cradle screw tips</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>B0DMCY4FN1</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>120</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§§9.5–9.7</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Lens-specific. Two locating walls and a countersunk M5 hole per yoke; two M5 side-channel clamp holes.</t>
+          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAM-009</t>
+          <t>CAM-010</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4876,30 +4881,30 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>N52 Bar Magnet - 10mm L x 5mm W x 2mm H</t>
+          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Flat bearing inserts under three lens-cradle screw tips</t>
+          <t>Groove rods at the fourth lens-cradle screw</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>B0DMCY4FN1</t>
+          <t>91585A351</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4918,14 +4923,14 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Nickel-plated rectangular magnets, 10 mm side across the rail; the fourth screw tip sits in a rod groove (CAM-010).</t>
+          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAM-010</t>
+          <t>CAM-011</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4938,52 +4943,34 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ø3 × 10 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
+          <t>PLA printed lens collars</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Groove rods at the fourth lens-cradle screw</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>91585A351</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>50</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>§§9.5–9.7</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Chamfered ends. Two installed, lying across the rail in the aft collar pad pocket; one pack of 50.</t>
+          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a flat bearing insert.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CAM-011</t>
+          <t>CAM-012</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4996,17 +4983,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PLA printed lens collars</t>
+          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Split clamps on the lens barrel, carrying the adjuster pads</t>
+          <t>Lens collar clamp screws</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>91292A114</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>100</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5016,14 +5021,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Two collars for the 37 mm barrel, identical except that the aft collar's left pad pocket seats the groove rods (CAM-010) in place of a flat bearing insert.</t>
+          <t>Shared common 100-pack. One screw per collar.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAM-012</t>
+          <t>CAM-013</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5036,12 +5041,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>M3 × 12 mm socket head screw, 18-8 SS</t>
+          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lens collar clamp screws</t>
+          <t>Lens collar clamp nuts</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5051,7 +5056,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>91292A114</t>
+          <t>91828A211</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -5074,14 +5079,14 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Shared common 100-pack. One screw per collar.</t>
+          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAM-013</t>
+          <t>CAM-014</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5094,12 +5099,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M3 × 0.5 hex nut, 18-8 SS, 5.5 mm AF × 2.4 mm high</t>
+          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lens collar clamp nuts</t>
+          <t>Lens cradle retaining bands</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5109,11 +5114,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>91828A211</t>
+          <t>9262K203</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5127,19 +5132,19 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§9.8</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Shared common 100-pack (see CAS-004). One nut per collar.</t>
+          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAM-014</t>
+          <t>CAM-015</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5152,52 +5157,34 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Oil-resistant Buna-N O-ring, 2 mm wide × 40 mm ID, 70A, round</t>
+          <t>PLA printed lens cradle yokes</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lens cradle retaining bands</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>9262K203</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>25</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Carry the adjuster inserts and the retaining-band pegs</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>§9.8</t>
+          <t>§9.5</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
+          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAM-015</t>
+          <t>CAM-016</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5210,34 +5197,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PLA printed lens cradle yokes</t>
+          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Carry the adjuster inserts and the retaining-band pegs</t>
+          <t>Yoke-to-shoe joint screws</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>92125A208</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>100</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>§9.5</t>
+          <t>§§9.5, 9.7</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Printed on their side; each bolted to the cradle shoe with one countersunk M5 screw (CAM-016) into a heat-set insert (CAM-005).</t>
+          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CAM-016</t>
+          <t>CAM-017</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5246,16 +5251,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M5 × 0.8 × 10 mm 18-8 stainless hex-drive flat head screw, 90°</t>
+          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yoke-to-shoe joint screws</t>
+          <t>Phone rest rod</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5265,11 +5270,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>92125A208</t>
+          <t>91585A457</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5283,24 +5288,24 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>§§9.5, 9.7</t>
+          <t>§9.6</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>10 mm head, 3 mm hex drive. Each screws up through the cradle shoe deck into a heat-set insert in the yoke foot.</t>
+          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CAM-017</t>
+          <t>MIR-001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Imager</t>
+          <t>Mirror cell</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5308,30 +5313,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ø4 × 20 mm 18-8 stainless dowel pin, ISO 2338 m6</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Phone rest rod</t>
+          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>91585A457</t>
+          <t>B0B5RR41CT</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5341,19 +5341,14 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>§9.6</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Chamfered ends. Lies along the rail in the half-round seat of the phone rest arm (CAM-007); one pack of 25.</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIR-001</t>
+          <t>MIR-002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5362,11 +5357,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Skyoptikst D203F1600 spherical mirror, Ø203 mm, f=1600 mm</t>
+          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Base and adjuster plates</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5376,15 +5376,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B0B5RR41CT</t>
+          <t>B09D941GXR</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIR-002</t>
+          <t>MIR-003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5410,16 +5410,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 1/2 in</t>
+          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Base and adjuster plates</t>
+          <t>Mirror plate</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5429,15 +5429,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>B09D941GXR</t>
+          <t>B0GL9G45GH</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MIR-003</t>
+          <t>MIR-004</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5463,30 +5463,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Baltic birch plywood panel 12 × 12 × 3/4 in</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Mirror plate</t>
+          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Kozak</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>B0GL9G45GH</t>
+          <t>TS250-80-2500</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5500,14 +5495,14 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>§10.1</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIR-004</t>
+          <t>MIR-005</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5520,7 +5515,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1/4-80 TPI Imperial fine adjustment screws, 2.5 in</t>
+          <t>Imperial Fine Adjustment Carrier Bushings</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5530,7 +5525,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TS250-80-2500</t>
+          <t>TB250-80-625</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -5555,7 +5550,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIR-005</t>
+          <t>MIR-006</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5568,7 +5563,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Imperial Fine Adjustment Carrier Bushings</t>
+          <t>Imperial Adjustment Knobs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5578,7 +5573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TB250-80-625</t>
+          <t>KB250-80</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -5603,7 +5598,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MIR-006</t>
+          <t>MIR-007</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5616,17 +5611,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Imperial Adjustment Knobs</t>
+          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Spherical washers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>KB250-80</t>
+          <t>91131A028</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -5644,14 +5644,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§10.4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MIR-007</t>
+          <t>MIR-008</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5664,12 +5664,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Leveling Washer, Two Piece, 1/4" Screw Size, Black-Oxide Steel</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Spherical washers</t>
+          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5679,15 +5674,15 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>91131A028</t>
+          <t>2022N186</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5697,14 +5692,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIR-008</t>
+          <t>MIR-009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5713,11 +5708,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Compression Springs, 0.75" Long, 0.5" OD, 0.424" ID</t>
+          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Spring seat washers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5727,11 +5727,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2022N186</t>
+          <t>98017A199</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MIR-009</t>
+          <t>MIR-010</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5761,16 +5761,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Washer for 3/8" washer, 0.390" ID, 0.028" to 0.036" thick, 18-8 SS</t>
+          <t>3" Long Corner Bracket, aluminum</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spring seat washers</t>
+          <t>Adjuster plate to base plate mounting</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5780,15 +5780,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>98017A199</t>
+          <t>8681N11</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MIR-010</t>
+          <t>MIR-012</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5814,11 +5814,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3" Long Corner Bracket, aluminum</t>
+          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5833,15 +5833,15 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8681N11</t>
+          <t>90099A030</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5852,13 +5852,18 @@
       <c r="K102" t="inlineStr">
         <is>
           <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MIR-012</t>
+          <t>MIR-013</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5871,7 +5876,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5/16"-18 heavy-profile nylon-insert locknut, 18-8 SS</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5886,11 +5891,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>90099A030</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5909,14 +5914,14 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Eight installed, four per bracket. Two 5-packs in hand (10 nuts, two spare).</t>
+          <t>Eight installed, one under each bracket locknut.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIR-013</t>
+          <t>MIR-024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5925,16 +5930,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
+          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Adjuster plate to base plate mounting</t>
+          <t>Quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5944,11 +5949,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>96659A134</t>
+          <t>92125A196</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5962,19 +5967,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>§10.7</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Eight installed, one under each bracket locknut.</t>
+          <t>Four installed.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MIR-024</t>
+          <t>MIR-025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5983,34 +5988,34 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 18 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Quick-release plate mounting screws</t>
+          <t>Mirror-cell quick-release / tripod interface</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>92125A196</t>
+          <t>B0B2WBC921</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6025,14 +6030,14 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Four installed.</t>
+          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MIR-025</t>
+          <t>MIR-019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6045,22 +6050,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CAMVATE Manfrotto-Type Quick Release Assembly with Sliding Plate Camera Mount</t>
+          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mirror-cell quick-release / tripod interface</t>
+          <t>Mirror mounting</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>B0B2WBC921</t>
+          <t>7587A25</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -6078,19 +6083,14 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>§10.9</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Complete 577/501/504-compatible quick-release assembly with removable sliding plate and receiver. The removable plate is drilled and tapped M4 to the §10.9 layout.</t>
+          <t>§10.5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIR-019</t>
+          <t>MIR-020</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DOWSIL 737 clear silicone, 3 fl. oz.</t>
+          <t>Adhesive backed F1 felt</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mirror mounting</t>
+          <t>Safety retainer padding</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>7587A25</t>
+          <t>8334K15</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6136,14 +6136,19 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>§10.5</t>
+          <t>§10.8</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIR-020</t>
+          <t>MIR-021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6152,56 +6157,28 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Adhesive backed F1 felt</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Safety retainer padding</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>8334K15</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>sheet</t>
+          <t>PLA printed front safety retainers</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD open</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>§10.8</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Provisional: facing for the safety retainers (MIR-021); the retainers are not yet designed.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MIR-021</t>
+          <t>MIR-026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6210,46 +6187,69 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PLA printed front safety retainers</t>
+          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Bracket screws, heads on the bracket</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>98164A527</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>5</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>CAD open</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>§10.8</t>
+          <t>§10.7</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MIR-026</t>
+          <t>SHP-001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mirror cell</t>
+          <t>Shop supplies</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" 316 stainless button-head hex-drive screw</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Bracket screws, heads on the bracket</t>
+          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6259,15 +6259,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>98164A527</t>
+          <t>91458A160</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6277,19 +6277,14 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>§10.7</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Four per bracket, two through the plate and two through the base; eight installed. 3/16 in hex drive; head Ø0.547 in × 0.166 in. Pushed through from the bracket side, with MIR-013 washers and MIR-012 locknuts behind the plywood. Thread projects about 0.12 in past the locknut.</t>
+          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHP-001</t>
+          <t>SHP-003</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6302,17 +6297,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Loctite 271 threadlocker, .34 fl. oz.</t>
+          <t>Optical spanner wrench</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>91458A160</t>
+          <t>B0CKSL364Q</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -6326,18 +6321,13 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>§9.7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SHP-003</t>
+          <t>SHP-004</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6350,7 +6340,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Optical spanner wrench</t>
+          <t>Metric feeler gauge set</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Source-slit blade spacing</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6360,7 +6355,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>B0CKSL364Q</t>
+          <t>B07XPD9L1C</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -6374,13 +6369,18 @@
       <c r="J112" t="inlineStr">
         <is>
           <t>In hand</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>§7.4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHP-004</t>
+          <t>SHP-005</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6393,22 +6393,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Metric feeler gauge set</t>
+          <t>M2 tap</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Source-slit blade spacing</t>
+          <t>LED board mounting into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>B07XPD9L1C</t>
+          <t>8305A78</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -6426,14 +6426,19 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>§7.4</t>
+          <t>§6.4</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHP-005</t>
+          <t>SHP-006</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6446,12 +6451,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>M2 tap</t>
+          <t>M2 tap drill, 1.6mm</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LED board mounting into SM1CP2M cap</t>
+          <t>LED mounting</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6461,7 +6466,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8305A78</t>
+          <t>2979N13</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -6480,18 +6485,13 @@
       <c r="K114" t="inlineStr">
         <is>
           <t>§6.4</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Plug chamfer; sufficient for the through M2 holes.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHP-006</t>
+          <t>SHP-011</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>M2 tap drill, 1.6mm</t>
+          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LED mounting</t>
+          <t>Plywood fiber conditioning and localized tack bonds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2979N13</t>
+          <t>1818A45</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -6537,14 +6537,19 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§§8.3, 8.4, 8.7, 10.4</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHP-011</t>
+          <t>SHP-012</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6557,22 +6562,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Loctite 4061 cyanoacrylate adhesive, 0.7 fl. oz., low viscosity (~20 cP)</t>
+          <t>UHMW Sheet 1/8" x 12" x 12"</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Plywood fiber conditioning and localized tack bonds</t>
+          <t>Mirror mount releasing assembly surface</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>US Plastics</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1818A45</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -6590,19 +6595,14 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>§§8.3, 8.4, 8.7, 10.4</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Use sparingly: wick into Baltic-birch fibers for the spherical-washer sockets (§10.4); needle-sized drops retain the carriage magnet pad and datum pins (§§8.3, 8.4) and keep the cassette clamp-bar screws captive (§8.7). No accelerator required.</t>
+          <t>§10.6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHP-012</t>
+          <t>SHP-014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6615,22 +6615,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>UHMW Sheet 1/8" x 12" x 12"</t>
+          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mirror mount releasing assembly surface</t>
+          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>US Plastics</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>B002IZFPQE</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -6648,14 +6648,14 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>§10.6</t>
+          <t>§10.2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHP-014</t>
+          <t>SHP-015</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6668,22 +6668,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>West System G/Flex 650 Epoxy Adhesive, 2 x 4 oz</t>
+          <t>Silicone grease, clear, NLGI 1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mirror cell adjuster sleeves, spring seat washer tack</t>
+          <t>PLA carriage sliding-interface lubricant</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>B002IZFPQE</t>
+          <t>1418K51</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -6701,14 +6701,19 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>§10.2</t>
+          <t>§8.4</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHP-015</t>
+          <t>SHP-016</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6721,22 +6726,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Silicone grease, clear, NLGI 1</t>
+          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PLA carriage sliding-interface lubricant</t>
+          <t>Light grease for mirror-cell spherical washer interfaces</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1418K51</t>
+          <t>B009XE8M3G</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -6754,19 +6759,19 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>§8.4</t>
+          <t>§10.4</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Use only a trace film on dressed PLA-on-PLA sliding interfaces.</t>
+          <t>Small tube to transport with the apparatus.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHP-016</t>
+          <t>SHP-017</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6779,22 +6784,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Dynatex 159375 White Lithium Grease NLGI 2</t>
+          <t>1/2" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Light grease for mirror-cell spherical washer interfaces</t>
+          <t>Spherical-washer counterbores</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>B009XE8M3G</t>
+          <t>2890A56</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -6817,14 +6822,14 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Small tube to transport with the apparatus.</t>
+          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHP-017</t>
+          <t>SHP-018</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6837,12 +6842,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1/2" Forstner bit, standard-point smooth-finish</t>
+          <t>5/8" Forstner bit, standard-point smooth-finish</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Spherical-washer counterbores</t>
+          <t>Spring-seat washer counterbores</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6852,7 +6857,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2890A56</t>
+          <t>2890A58</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -6870,19 +6875,19 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>§10.4</t>
+          <t>§10.3</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow close-fit spherical-washer sockets; test in scrap Baltic birch before cutting final plate.</t>
+          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHP-018</t>
+          <t>SHP-019</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6895,12 +6900,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5/8" Forstner bit, standard-point smooth-finish</t>
+          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spring-seat washer counterbores</t>
+          <t>Tap CAMVATE quick-release plate mounting holes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6910,7 +6915,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2890A58</t>
+          <t>1021N23</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -6928,19 +6933,19 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>§10.3</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Use in drill press for shallow spring-seat-washer registration counterbores; test depth/fit in scrap first.</t>
+          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHP-019</t>
+          <t>SHP-020</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6953,12 +6958,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M4 × 0.7 high-speed-steel plug-chamfer hex-bit tap</t>
+          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tap CAMVATE quick-release plate mounting holes</t>
+          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6968,7 +6973,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1021N23</t>
+          <t>2958A64</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -6986,19 +6991,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§6.4, 10.9</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Use with the 3.3 mm tap drill (SHP-020); hole locations in §10.9.</t>
+          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHP-020</t>
+          <t>SHP-021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7011,12 +7016,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3.3 mm black-oxide HSS jobber-length drill bit</t>
+          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>M4 × 0.7 tap drill for CAMVATE quick-release plate; M3 heatsink clearance holes</t>
+          <t>Removable thread retention for quick-release plate mounting screws</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7026,7 +7031,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2958A64</t>
+          <t>91458A115</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -7044,19 +7049,19 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>§§6.4, 10.9</t>
+          <t>§10.9</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Standard 3.3 mm tap-drill size for M4 × 0.7. Also drills the Ø3.3 M3 clearance holes in the heatsink base (§6.4).</t>
+          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHP-021</t>
+          <t>SHP-022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7069,22 +7074,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Loctite 243 medium-strength removable threadlocker, 0.34 fl. oz.</t>
+          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Removable thread retention for quick-release plate mounting screws</t>
+          <t>Opaque masking / thin-sheet cutoff experiments</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Fullcompass</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>91458A115</t>
+          <t>01001-1210</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -7092,7 +7097,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7102,19 +7107,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>§10.9</t>
+          <t>§§8.6, 8.7</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Apply only after the screw fit is confirmed (the hole sizes are provisional, §10.9); preferred over high-strength Loctite 271 for this serviceable joint.</t>
+          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHP-022</t>
+          <t>SHP-023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7127,22 +7132,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Rosco Photofoil matte black aluminum wrap, 12"x10'</t>
+          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Opaque masking / thin-sheet cutoff experiments</t>
+          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fullcompass</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>01001-1210</t>
+          <t>8305A32</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -7150,7 +7155,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7160,19 +7165,19 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>§§8.6, 8.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Retained as general shop stock for opaque masking and thin-sheet cutoff experiments.</t>
+          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHP-023</t>
+          <t>SHP-025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7185,12 +7190,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>M3 × 0.5 high-speed-steel plug-chamfer tap, 5/8" thread length</t>
+          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tap through M3 heatsink-screw holes in SM1CP2M cap</t>
+          <t>M3 tap drill for through holes in SM1CP2M cap</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7200,7 +7205,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8305A32</t>
+          <t>2979N15</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -7223,14 +7228,14 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All holes are through holes, so a plug chamfer is enough; no bottoming tap needed. Use with the 2.5 mm tap drill (SHP-025).</t>
+          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHP-025</t>
+          <t>SHP-026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7243,35 +7248,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2.5 mm TiN-coated HSS short-length drill bit, 43 mm overall</t>
+          <t>2mm Premium High Speed Steel Jobber Length Drill, 10 pack</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>M3 tap drill for through holes in SM1CP2M cap</t>
+          <t>Lead holes through SM1CP2M cap and heatsink base</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2979N15</t>
+          <t>B07211L28S</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7281,14 +7286,14 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Short-length stub drill for rigid drilling in the thin cap; same series as the 1.6 mm drill SHP-006.</t>
+          <t>Lead holes (§6.4): the pigtail wire measures about 1.7 mm over its insulation. McMaster alternative if wanted later: 2979N14, 2.0 mm uncoated HSS short-length drill bit, 38 mm overall (same series as the 1.6 mm drill SHP-006).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHP-026</t>
+          <t>SHP-027</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7301,52 +7306,52 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2mm Premium High Speed Steel Jobber Length Drill, 10 pack</t>
+          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lead holes through SM1CP2M cap and heatsink base</t>
+          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>B07211L28S</t>
+          <t>8915N111</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§9.7</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Lead holes (§6.4): the pigtail wire measures about 1.7 mm over its insulation. McMaster alternative if wanted later: 2979N14, 2.0 mm uncoated HSS short-length drill bit, 38 mm overall (same series as the 1.6 mm drill SHP-006).</t>
+          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed). Replaces the 1/4 in plug tip UNU-011. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHP-027</t>
+          <t>SHP-028</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7359,22 +7364,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Heat-set insert installation tip set, 8 pieces (M2 to M8) with 1/4 in shank adapter</t>
+          <t>Hakko FX888DX-10 soldering station</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Fits a Hakko 900M-style iron; M5 tip sets the CAM-005 inserts</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>McMaster</t>
+          <t>Heat-set insert installation (CAM-005)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8915N111</t>
+          <t>FX888DX-10</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -7397,14 +7397,14 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Listed for Hakko 900M. The M5 tip has a female threaded connection and mounts through the included adapter, which fits the Hakko iron (confirmed). Replaces the 1/4 in plug tip UNU-011. Used with the Hakko iron SHP-028; set PLA installation near 200–230 °C (typical for PLA; confirm on a scrap print), no higher than 250 °C.</t>
+          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-028</t>
+          <t>SHP-029</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7417,17 +7417,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Hakko FX888DX-10 soldering station</t>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Heat-set insert installation (CAM-005)</t>
+          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FX888DX-10</t>
+          <t>27445A201</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7445,19 +7450,19 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§9.7</t>
+          <t>§6.4</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Vendor not recorded here. Takes Hakko T18 (900M-style) tips. Drives the SHP-027 tip set; the SHP-027 adapter fits the iron (confirmed).</t>
+          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-029</t>
+          <t>SHP-030</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7470,12 +7475,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+          <t>Backup hole spotter; spots the cap and heatsink holes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7485,7 +7490,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>27445A201</t>
+          <t>2915A11</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7508,46 +7513,43 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
+          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-030</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>1</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Backup hole spotter; spots the cap and heatsink holes</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2915A11</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7559,21 +7561,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>§6.4</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNU-001</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7583,26 +7580,26 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>Existing stock; former carriage-tube allocation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>SM1L15</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7616,14 +7613,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNU-002</t>
+          <t>UNU-003</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7633,22 +7630,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>Existing stock; former spring guide / retract handle</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>91273A377</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -7666,14 +7663,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNU-003</t>
+          <t>UNU-005</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7683,12 +7680,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7698,15 +7695,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7716,14 +7713,14 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNU-005</t>
+          <t>UNU-006</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7733,12 +7730,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7748,15 +7745,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7766,14 +7763,14 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNU-006</t>
+          <t>UNU-007</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7783,7 +7780,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7798,15 +7795,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7823,7 +7820,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNU-007</t>
+          <t>UNU-008</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7833,7 +7830,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7848,11 +7845,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -7873,7 +7870,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNU-008</t>
+          <t>UNU-009</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7883,12 +7880,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7898,11 +7895,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -7916,14 +7913,14 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNU-009</t>
+          <t>UNU-010</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7933,12 +7930,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7948,11 +7945,11 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7966,14 +7963,14 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UNU-010</t>
+          <t>UNU-011</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7983,12 +7980,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7998,15 +7990,15 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8016,14 +8008,14 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UNU-011</t>
+          <t>UNU-012</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8033,7 +8025,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Existing spare stock; former LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8043,15 +8040,15 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>92095A452</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8061,7 +8058,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
+          <t>No longer allocated: 5 mm was a bit short; replaced by LGT-020 (92095A453 M2 × 6 mm).</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$L$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$L$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Also faces the two slit-head blade clamp bars (§7.5).</t>
+          <t>Also faces the two slit-head blade clamp bars (§7.5), and supplies the Ø10 mm hold-down disc under the drilling-fixture plate (§6.8).</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Eight installed, one under each bracket locknut.</t>
+          <t>Eight installed, one under each bracket locknut. Two more from the pack in SHP-038.</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>On order</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7520,36 +7520,39 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNU-001</t>
+          <t>SHP-031</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>Metric press-fit drill bushing, 1.6 mm ID, 4 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>M2 tap-drill positions in the drilling fixture plate</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>96990A132</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7558,48 +7561,56 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNU-002</t>
+          <t>SHP-032</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>3</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>Metric press-fit drill bushing, 2.5 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>M3 tap-drill positions in the cap, M3 pilot positions in the heatsink</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>96990A147</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7608,34 +7619,42 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNU-003</t>
+          <t>SHP-033</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>Metric press-fit drill bushing, 2 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Lead-hole positions in the cap and the heatsink base</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7645,11 +7664,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>96990A139</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -7658,84 +7677,82 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNU-005</t>
+          <t>SHP-034</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>PLA printed LED-module drilling fixture</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>90585A587</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>5</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>pack</t>
+          <t>Bushing plate, cap nest, and heatsink nest for drilling the SM1CP2M cap and CN40-40B heatsink</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>CAD ready</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>Set of three prints, plus a bore coupon to print first (sets the bushing bore size). Fastened with five M3 × 12 mm screws (four plate corners, one cap clamp) from the common 100-pack (SLT-007), into five M3 heat-set inserts (SHP-035) set in the nests.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNU-006</t>
+          <t>SHP-035</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>5</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>Brass flanged heat-set threaded inserts for plastic, M3 × 0.5 mm, 5.7 mm installed length</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Plate screws (4) and cap clamp screw (1) in the drilling fixture nests</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7745,47 +7762,55 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>97171A310</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Ø4 mm hole, Ø5.5 mm flange recessed. Set with the M3 tip of the SHP-027 tip set on the Hakko iron (SHP-028); the M3 tip is not yet confirmed to be in the set. Forty-five spare.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNU-007</t>
+          <t>SHP-036</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>5/16"-18 × 1-1/4" 18-8 stainless square-neck carriage bolt</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Drilling fixture mounting: bolts in the drill-press base slots</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7795,11 +7820,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>92356A589</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -7808,34 +7833,42 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Head under the base, 0.32" square neck in the 3/8" base slot; one per nest ear, two used at a time.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNU-008</t>
+          <t>SHP-037</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>5/16"-18 18-8 stainless flanged knurled-head thumb nut</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Drilling fixture mounting: clamp the nest ears from the top</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7845,47 +7878,55 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>95150A180</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>5/8" knurled head, 17/32" collar on the washer.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNU-009</t>
+          <t>SHP-038</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Unused</t>
-        </is>
+          <t>Shop supplies</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Drilling fixture mounting: under the thumb nuts on the nest ears</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7895,11 +7936,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -7911,16 +7952,21 @@
           <t>In hand</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>§6.8</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>Shared 25-pack with MIR-013 (eight used there).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNU-010</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7930,30 +7976,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7963,14 +8009,14 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UNU-011</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7980,21 +8026,26 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Existing stock; former carriage-tube allocation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>SM1L15</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8008,63 +8059,458 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>UNU-003</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Existing stock; former spring guide / retract handle</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>91273A377</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>UNU-005</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Existing alternate/fallback bracket screw stock</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>90585A587</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>5</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>UNU-006</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>94518A525</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>4</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>UNU-007</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1/4"-20 flex-top locknuts</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>91839A123</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>5</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>UNU-008</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1/4" thin washers</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>98019A255</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>10</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>UNU-009</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Existing alternate bracket screw stock</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>90585A997</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>5</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>UNU-010</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>92125A194</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>100</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>UNU-011</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Heat-set installation tip</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>92160A327</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>UNU-012</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Unused</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>Existing spare stock; former LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>McMaster</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>92095A452</t>
         </is>
       </c>
-      <c r="H143" t="n">
+      <c r="H151" t="n">
         <v>25</v>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>pack</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>In hand</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>In hand</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t>No longer allocated: 5 mm was a bit short; replaced by LGT-020 (92095A453 M2 × 6 mm).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L143"/>
-  <conditionalFormatting sqref="J2:J143">
+  <autoFilter ref="A1:L151"/>
+  <conditionalFormatting sqref="J2:J151">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"In hand"</formula>
     </cfRule>
@@ -8081,13 +8527,13 @@
       <formula>"CAD open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:L143">
+  <conditionalFormatting sqref="A2:L151">
     <cfRule type="expression" priority="6" dxfId="5">
       <formula>$B2&lt;&gt;$B1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J143" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J151" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"In hand,On order,To procure,Specified,CAD ready,CAD open"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -7404,7 +7404,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHP-029</t>
+          <t>SHP-031</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7413,16 +7413,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+          <t>Metric press-fit drill bushing, 1.6 mm ID, 4 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Spot hole locations in the SM1CP2M cap and heatsink base before drilling</t>
+          <t>M2 tap-drill positions in the drilling fixture plate</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>27445A201</t>
+          <t>96990A132</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -7445,24 +7445,24 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>1/8" shank fits the Dremel 4486 chuck (1/8" maximum). Use before the 1.6, 2.0, 2.5, and 3.3 mm drills.</t>
+          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHP-030</t>
+          <t>SHP-032</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7471,16 +7471,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
+          <t>Metric press-fit drill bushing, 2.5 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Backup hole spotter; spots the cap and heatsink holes</t>
+          <t>M3 tap-drill positions in the cap, M3 pilot positions in the heatsink</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2915A11</t>
+          <t>96990A147</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -7503,24 +7503,24 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>In hand</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>§6.4</t>
+          <t>§6.8</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>3/64" pilot, 1/8" body; fits the Dremel 4486 chuck. Spare for SHP-029.</t>
+          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHP-031</t>
+          <t>SHP-033</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Metric press-fit drill bushing, 1.6 mm ID, 4 mm OD, 6 mm long, chamfer on one end</t>
+          <t>Metric press-fit drill bushing, 2 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>M2 tap-drill positions in the drilling fixture plate</t>
+          <t>Lead-hole positions in the cap and the heatsink base</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>96990A132</t>
+          <t>96990A139</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -7578,7 +7578,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHP-032</t>
+          <t>SHP-034</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7587,39 +7587,21 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Metric press-fit drill bushing, 2.5 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
+          <t>PLA printed LED-module drilling fixture</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>M3 tap-drill positions in the cap, M3 pilot positions in the heatsink</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>96990A147</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
-        <v>1</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>each</t>
+          <t>Bushing plate, cap nest, and heatsink nest for drilling the SM1CP2M cap and CN40-40B heatsink</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>CAD ready</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -7629,14 +7611,14 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
+          <t>Set of three prints, plus a bore coupon to print first (sets the bushing bore size). Fastened with five M3 × 12 mm screws (four plate corners, one cap clamp) from the common 100-pack (SLT-007), into five M3 heat-set inserts (SHP-035) set in the nests.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHP-033</t>
+          <t>SHP-035</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7645,16 +7627,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Metric press-fit drill bushing, 2 mm ID, 5 mm OD, 6 mm long, chamfer on one end</t>
+          <t>Brass flanged heat-set threaded inserts for plastic, M3 × 0.5 mm, 5.7 mm installed length</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lead-hole positions in the cap and the heatsink base</t>
+          <t>Plate screws (4) and cap clamp screw (1) in the drilling fixture nests</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7664,15 +7646,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>96990A139</t>
+          <t>97171A310</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7687,14 +7669,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Hardened steel, headless. Pressed into the printed bushing plate (SHP-034). No spare in the quantity.</t>
+          <t>Ø4 mm hole, Ø5.5 mm flange recessed. Set with the M3 tip of the SHP-027 tip set on the Hakko iron (SHP-028); the M3 tip is not yet confirmed to be in the set. Forty-five spare.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHP-034</t>
+          <t>SHP-036</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7703,21 +7685,39 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PLA printed LED-module drilling fixture</t>
+          <t>5/16"-18 × 1-1/4" 18-8 stainless square-neck carriage bolt</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bushing plate, cap nest, and heatsink nest for drilling the SM1CP2M cap and CN40-40B heatsink</t>
+          <t>Drilling fixture mounting: bolts in the drill-press base slots</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>92356A589</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>10</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>CAD ready</t>
+          <t>To procure</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Set of three prints, plus a bore coupon to print first (sets the bushing bore size). Fastened with five M3 × 12 mm screws (four plate corners, one cap clamp) from the common 100-pack (SLT-007), into five M3 heat-set inserts (SHP-035) set in the nests.</t>
+          <t>Head under the base, 0.32" square neck in the 3/8" base slot; one per nest ear, two used at a time.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHP-035</t>
+          <t>SHP-037</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7743,16 +7743,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Brass flanged heat-set threaded inserts for plastic, M3 × 0.5 mm, 5.7 mm installed length</t>
+          <t>5/16"-18 18-8 stainless flanged knurled-head thumb nut</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Plate screws (4) and cap clamp screw (1) in the drilling fixture nests</t>
+          <t>Drilling fixture mounting: clamp the nest ears from the top</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7762,15 +7762,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>97171A310</t>
+          <t>95150A180</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Ø4 mm hole, Ø5.5 mm flange recessed. Set with the M3 tip of the SHP-027 tip set on the Hakko iron (SHP-028); the M3 tip is not yet confirmed to be in the set. Forty-five spare.</t>
+          <t>5/8" knurled head, 17/32" collar on the washer.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SHP-036</t>
+          <t>SHP-038</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-1/4" 18-8 stainless square-neck carriage bolt</t>
+          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Drilling fixture mounting: bolts in the drill-press base slots</t>
+          <t>Drilling fixture mounting: under the thumb nuts on the nest ears</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7820,11 +7820,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>92356A589</t>
+          <t>96659A134</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -7843,46 +7843,43 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Head under the base, 0.32" square neck in the 3/8" base slot; one per nest ear, two used at a time.</t>
+          <t>Shared 25-pack with MIR-013 (eight used there).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SHP-037</t>
+          <t>UNU-001</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>2</v>
+          <t>Unused</t>
+        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5/16"-18 18-8 stainless flanged knurled-head thumb nut</t>
+          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Drilling fixture mounting: clamp the nest ears from the top</t>
+          <t>Existing spare stock; former LED heatsink</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>McMaster</t>
+          <t>HeatsinkOnline</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>95150A180</t>
+          <t>64ASL-8-55</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -7891,60 +7888,52 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>To procure</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>§6.8</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>5/8" knurled head, 17/32" collar on the washer.</t>
+          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SHP-038</t>
+          <t>UNU-002</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shop supplies</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SM1 lens tube, 1.50" Thread Depth</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Existing stock; former carriage-tube allocation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Thorlabs</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SM1L15</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
         <v>2</v>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>5/16" SAE washer, 0.344" ID × 0.688" OD, 18-8 SS black oxide</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Drilling fixture mounting: under the thumb nuts on the nest ears</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>McMaster</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>96659A134</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>25</v>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7952,21 +7941,16 @@
           <t>In hand</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>§6.8</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Shared 25-pack with MIR-013 (eight used there).</t>
+          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNU-001</t>
+          <t>UNU-003</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7976,26 +7960,26 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Heatsink, 6063-T5 non-anodized aluminum, Ø55 mm x 20 mm.</t>
+          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED heatsink</t>
+          <t>Existing stock; former spring guide / retract handle</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HeatsinkOnline</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>64ASL-8-55</t>
+          <t>91273A377</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -8009,14 +7993,14 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No longer allocated after the threaded SM1 LED module decision; replaced by LGT-018 (Alpha CN40-40B). Four in hand retained as spares.</t>
+          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UNU-002</t>
+          <t>UNU-005</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8026,30 +8010,30 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SM1 lens tube, 1.50" Thread Depth</t>
+          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Existing stock; former carriage-tube allocation</t>
+          <t>Existing alternate/fallback bracket screw stock</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Thorlabs</t>
+          <t>McMaster</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SM1L15</t>
+          <t>90585A587</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8059,14 +8043,14 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>No longer allocated: the cutoff carriage mounts in the SM1RC/M on an integral printed spigot (§8.1); both tubes in hand are spare.</t>
+          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UNU-003</t>
+          <t>UNU-006</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8076,12 +8060,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4 mm × 45 mm shoulder screw, 18-8 SS</t>
+          <t>1/4"-20 × 1-1/2" flat-head screws</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Existing stock; former spring guide / retract handle</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8091,11 +8075,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>91273A377</t>
+          <t>94518A525</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8109,14 +8093,14 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No longer allocated: the spring seats in printed cups and the plunger retracts by a thumb tab (§8.5); both screws in hand are spare.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UNU-005</t>
+          <t>UNU-007</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8126,12 +8110,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5/16" × 1-1/2" hex-drive flat-head screw, 316 SS</t>
+          <t>1/4"-20 flex-top locknuts</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Existing alternate/fallback bracket screw stock</t>
+          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8141,7 +8125,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>90585A587</t>
+          <t>91839A123</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -8159,14 +8143,14 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Previously baseline bracket screw; retained as in-hand alternate stock after corner-clearance review.</t>
+          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UNU-006</t>
+          <t>UNU-008</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8176,7 +8160,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1/4"-20 × 1-1/2" flat-head screws</t>
+          <t>1/4" thin washers</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8191,15 +8175,15 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>94518A525</t>
+          <t>98019A255</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8216,7 +8200,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UNU-007</t>
+          <t>UNU-009</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8226,12 +8210,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1/4"-20 flex-top locknuts</t>
+          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing alternate bracket screw stock</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8241,7 +8225,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>91839A123</t>
+          <t>90585A997</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -8259,14 +8243,14 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UNU-008</t>
+          <t>UNU-010</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8276,12 +8260,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1/4" thin washers</t>
+          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Existing spare stock; former C2564 tripod-interface hardware</t>
+          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8291,11 +8275,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>98019A255</t>
+          <t>92125A194</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8309,14 +8293,14 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>No longer allocated to the active tripod interface after transition to the CAMVATE 577/501/504 quick-release system; retain as in-hand spare hardware.</t>
+          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>UNU-009</t>
+          <t>UNU-011</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8326,12 +8310,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>5/16"-18 × 1-3/8" hex-drive flat-head screw, 316 SS</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Existing alternate bracket screw stock</t>
+          <t>Heat-set installation tip</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8341,15 +8320,15 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>90585A997</t>
+          <t>92160A327</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8359,14 +8338,14 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Former baseline bracket screw; retained as in-hand alternate stock after the change to button-head screws (MIR-026).</t>
+          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>UNU-010</t>
+          <t>UNU-012</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8376,12 +8355,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>M4 × 0.7 × 16 mm 90° flat-head hex-drive screw, 18-8 stainless</t>
+          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Existing spare stock; short-length alternative quick-release plate screw</t>
+          <t>Existing spare stock; former LED board mounting screws, tapped into SM1CP2M cap</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8391,11 +8370,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>92125A194</t>
+          <t>92095A452</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8409,14 +8388,14 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Not allocated: the quick-release plate takes the 18 mm screw (MIR-024); this pack is spare.</t>
+          <t>No longer allocated: 5 mm was a bit short; replaced by LGT-020 (92095A453 M2 × 6 mm).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UNU-011</t>
+          <t>UNU-013</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8426,7 +8405,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Heat-set installation tip</t>
+          <t>Hole-starting cobalt-steel drill bit, uncoated, 90° point, 1/8" size</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Existing spare stock; former hole spotter</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8436,7 +8420,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>92160A327</t>
+          <t>27445A201</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -8450,18 +8434,13 @@
       <c r="J150" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>No longer allocated; replaced by the SHP-027 tip set (8915N111), whose adapter is verified on the Hakko iron.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UNU-012</t>
+          <t>UNU-014</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8471,12 +8450,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>M2 × 5 mm button head hex-drive screw 18-8 SS</t>
+          <t>Center drill, high-speed steel, 60° countersink, trade size 1, 1-1/4" overall length</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Existing spare stock; former LED board mounting screws, tapped into SM1CP2M cap</t>
+          <t>Existing spare stock; former hole spotter</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8486,25 +8465,20 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>92095A452</t>
+          <t>2915A11</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>each</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>In hand</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>No longer allocated: 5 mm was a bit short; replaced by LGT-020 (92095A453 M2 × 6 mm).</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -5137,7 +5137,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated, modulus assumed). If too tight, 41 mm ID is McMaster 9262K694 (pack of 50).</t>
+          <t>One endless ring per collar, on the bare barrel beside the yoke and hooked on its peg. About 19% stretch gives about 3 N per leg (calculated). Test fit and accepted.</t>
         </is>
       </c>
     </row>

--- a/bom/schlieren-bom.xlsx
+++ b/bom/schlieren-bom.xlsx
@@ -7445,7 +7445,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Ø4 mm hole, Ø5.5 mm flange recessed. Set with the M3 tip of the SHP-027 tip set on the Hakko iron (SHP-028); the M3 tip is not yet confirmed to be in the set. Forty-five spare.</t>
+          <t>Ø4 mm hole, Ø5.5 mm flange recessed. Set with the M3 tip of the SHP-027 tip set on the Hakko iron (SHP-028). Forty-five spare.</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>In hand</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>To procure</t>
+          <t>On order</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
